--- a/submissions/08-nutrition-panel-granola/solution/oat_cherry_bar_label_review.xlsx
+++ b/submissions/08-nutrition-panel-granola/solution/oat_cherry_bar_label_review.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39CBCD2-830D-0946-B567-5596CC5671B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A199CD1A-C115-4D41-B8C7-F67E77C33416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="240">
   <si>
     <t>Nutrition Facts, Oat and Cherry Bar, formula OCB-26-03, as the wrapper will print</t>
   </si>
@@ -342,28 +342,19 @@
     <t>Whole grain rolled oats</t>
   </si>
   <si>
-    <t>whole grain rolled oats</t>
-  </si>
-  <si>
     <t>RM-2210</t>
   </si>
   <si>
     <t>Brown rice syrup</t>
   </si>
   <si>
-    <t>brown rice syrup</t>
-  </si>
-  <si>
     <t>RM-1187</t>
   </si>
   <si>
     <t>Crisp rice</t>
   </si>
   <si>
-    <t>crisp rice</t>
-  </si>
-  <si>
-    <t>rice flour, sugar, salt</t>
+    <t>rice, sugar, barley malt extract, salt</t>
   </si>
   <si>
     <t>RM-2205</t>
@@ -372,19 +363,13 @@
     <t>Clover honey</t>
   </si>
   <si>
-    <t>honey</t>
-  </si>
-  <si>
     <t>RM-3301</t>
   </si>
   <si>
     <t>Infused dried cherries</t>
   </si>
   <si>
-    <t>dried cherries</t>
-  </si>
-  <si>
-    <t>cherries, sugar, sunflower oil</t>
+    <t>tart cherries, sugar, sunflower oil</t>
   </si>
   <si>
     <t>RM-3120</t>
@@ -393,18 +378,12 @@
     <t>Roasted almond butter</t>
   </si>
   <si>
-    <t>almond butter</t>
-  </si>
-  <si>
     <t>RM-3115</t>
   </si>
   <si>
     <t>Sliced almonds</t>
   </si>
   <si>
-    <t>sliced almonds</t>
-  </si>
-  <si>
     <t>RM-4010</t>
   </si>
   <si>
@@ -420,51 +399,39 @@
     <t>High oleic sunflower oil</t>
   </si>
   <si>
-    <t>sunflower oil</t>
-  </si>
-  <si>
     <t>RM-5020</t>
   </si>
   <si>
     <t>Vanilla extract</t>
   </si>
   <si>
-    <t>natural vanilla flavor</t>
-  </si>
-  <si>
     <t>RM-5031</t>
   </si>
   <si>
     <t>Ground cinnamon</t>
   </si>
   <si>
-    <t>cinnamon</t>
-  </si>
-  <si>
     <t>RM-5040</t>
   </si>
   <si>
     <t>Sea salt</t>
   </si>
   <si>
-    <t>sea salt</t>
-  </si>
-  <si>
     <t>RM-5055</t>
   </si>
   <si>
     <t>Soy lecithin</t>
   </si>
   <si>
-    <t>soy lecithin</t>
-  </si>
-  <si>
     <t>Batch total</t>
   </si>
   <si>
     <t>Grams per serving are batch kilograms over the finished batch weight times the serving weight, per SOP 1.1 and 1.3; the water leaves in the bake, so the sum of the grams exceeds the serving weight by the water and volatiles lost.</t>
   </si>
   <si>
+    <t>DECLARED_NAME is the common name on the formula in lower case under SOP 4.1; SUB_INGREDIENTS are typed from specification S-1187 revision 7 for the crisp rice and specification S-3301 revision 5 for the cherries, in the order each lists them.</t>
+  </si>
+  <si>
     <t>Supplier nutrient specifications, ingredient_nutrient_specs.csv, and the same values normalised to 100 g per SOP 1.2</t>
   </si>
   <si>
@@ -681,7 +648,7 @@
     <t>Ingredients declared</t>
   </si>
   <si>
-    <t>Water is left off under SOP 4.1 because it is removed in the bake. The almonds are named as the specific tree nut under 4.2, and the soy lecithin carries the soy declaration.</t>
+    <t>Water is left off under SOP 4.1 because it is removed in the bake. The almonds are named as the specific tree nut under 4.2, and the soy lecithin carries the soy declaration. The barley malt extract in the crisp rice is a gluten source and not a major food allergen, and specification S-1187 states that none is present in the product, so the Contains statement stays at almonds and soy.</t>
   </si>
   <si>
     <t>Each claim in the product brief tested under SOP QA-14 section 5 on the unrounded amount per reference amount and per serving</t>
@@ -750,7 +717,7 @@
     <t>No sugar, syrup, honey or other sugar-bearing ingredient added</t>
   </si>
   <si>
-    <t>SOP 5.2; brown rice syrup, honey and sugar-infused cherries are added, and the panel declares the added sugars shown</t>
+    <t>SOP 5.2; brown rice syrup, honey, sugar-infused cherries and the sugar in the crisp rice are added, and the panel declares the added sugars shown</t>
   </si>
   <si>
     <t>Real fruit</t>
@@ -780,16 +747,16 @@
     <t>The cherries drive the added sugars line. Specification S-3301 revision 5 puts 30.0 g of the 60.0 g of sugars per 100 g as added, the sucrose taken up in the infusion, and revision 5 is the specification in force for every lot we hold, so the panel uses it. With the brown rice syrup and honey the bar carries 7.851 g of added sugars unrounded, declared as 8 g at 16 percent of the daily value, against 9.498 g of total sugars declared as 9 g. The percent daily values are computed from the declared, rounded amount under section 3.1, which is why the added sugars line shows 16 percent and not 15.7.</t>
   </si>
   <si>
-    <t>The ingredient statement lists twelve ingredients in descending order of formula weight with water left off under section 4.1, and it reads: Whole grain rolled oats, brown rice syrup, crisp rice (rice flour, sugar, salt), honey, dried cherries (cherries, sugar, sunflower oil), almond butter, sliced almonds, sunflower oil, natural vanilla flavor, cinnamon, sea salt, soy lecithin. The Contains statement reads Contains almonds and soy. The formula declares the vanilla extract as natural vanilla flavor; vanilla extract has its own standard of identity, so legal should confirm which name prints before the copy locks.</t>
+    <t>The ingredient statement lists twelve ingredients in descending order of formula weight with water left off under section 4.1, each under its common name on the formula, and it reads: Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract, ground cinnamon, sea salt, soy lecithin. The two compound ingredients carry the sub-ingredients their specifications list, S-1187 revision 7 for the crisp rice and S-3301 revision 5 for the cherries. The Contains statement reads Contains almonds and soy; the barley malt extract in the crisp rice is a gluten source and not a major food allergen, and S-1187 states that none is present in the product.</t>
   </si>
   <si>
     <t>On the claims. Good source of fiber is not supported. The panel declares 3 g of fiber at 11 percent of the daily value, because the declared value rounds up from 2.613 g, but section 5.1 tests the claim on the unrounded amount per reference amount and per serving, and the bar carries 2.489 g per 40 g reference amount, which is 8.9 percent of the daily value, and 9.3 percent per 42 gram serving. Both fall short of 10 percent, so the claim cannot go on the wrapper as the formula stands. It would take 2.8 g of fiber per 40 g to clear. Low sodium is supported at 123 mg per reference amount and 129.1 mg per serving against the 140 mg ceiling.</t>
   </si>
   <si>
-    <t>Made with whole grain oats is supported as a company statement under section 5.3: the bar carries 15.50 g of whole grain rolled oats per serving against the 8 gram floor. No artificial flavors is supported; the only flavoring in the formula is the vanilla extract, which the supplier specification states as a natural extract. Real fruit is supported on the dried tart cherries, 3.76 g per bar. No added sugar is not supported and cannot be: the formula adds brown rice syrup, honey and sugar-infused cherries, and the panel declares 8 g of added sugars, so section 5.2 rules the flag out however it is worded.</t>
-  </si>
-  <si>
-    <t>Things for you to decide or take to a supplier before the copy locks. First, the fiber claim comes off the front panel unless product development reopens the frozen formula; the nearest lift is the oats, and that is a formula change, not a wording change. Second, the no added sugar flag comes off; the sales lead should hear the 8 g figure rather than a softer claim. Third, the allergen line rests on the formula alone. The file carries no statement of what else runs on the co-packer line, so QA should confirm whether a shared-line advisory is needed before the wrapper prints. Fourth, the crisp rice supplier should confirm the S-1187 basis in writing, because the whole sodium line moves if that specification is read the other way. The workbook cites every specification revision it used on the Specs tab.</t>
+    <t>Made with whole grain oats is supported as a company statement under section 5.3: the bar carries 15.50 g of whole grain rolled oats per serving against the 8 gram floor. No artificial flavors is supported; the only flavorings in the formula are the vanilla extract, which specification S-5020 states as a natural extract, and the barley malt extract inside the crisp rice, which S-1187 states is its only flavoring. Real fruit is supported on the dried tart cherries, 3.76 g per bar. No added sugar is not supported and cannot be: the formula adds brown rice syrup, honey, sugar-infused cherries and a crisp rice that carries sugar of its own, and the panel declares 8 g of added sugars, so section 5.2 rules the flag out however it is worded.</t>
+  </si>
+  <si>
+    <t>Things for you to decide or take to a supplier before the copy locks. First, the fiber claim comes off the front panel unless product development reopens the frozen formula; the nearest lift is the oats, and that is a formula change, not a wording change. Second, the no added sugar flag comes off; the sales lead should hear the 8 g figure rather than a softer claim. Third, the Contains statement rests on the formula and the two specifications, and neither wheat nor barley belongs in it. S-1187 says the crisp rice packing line also runs a wheat flake cereal with a swab between runs, and the file carries no statement of what else runs on our co-packer line. QA should decide whether a shared-line advisory prints under the Contains statement before the wrapper goes. The workbook cites every specification revision it used on the Specs tab.</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1149,7 @@
     <col min="5" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1511,7 +1478,7 @@
       </c>
       <c r="B22" t="str">
         <f>'Ingredient Statement'!B17</f>
-        <v>Whole grain rolled oats, brown rice syrup, crisp rice (rice flour, sugar, salt), honey, dried cherries (cherries, sugar, sunflower oil), almond butter, sliced almonds, sunflower oil, natural vanilla flavor, cinnamon, sea salt, soy lecithin.</v>
+        <v>Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract, ground cinnamon, sea salt, soy lecithin.</v>
       </c>
       <c r="E22" t="s">
         <v>32</v>
@@ -1571,44 +1538,44 @@
     <col min="1" max="1" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="64" x14ac:dyDescent="0.2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="64" x14ac:dyDescent="0.2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="64" x14ac:dyDescent="0.2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="64" x14ac:dyDescent="0.2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="80" x14ac:dyDescent="0.2">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="64" x14ac:dyDescent="0.2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="96" x14ac:dyDescent="0.2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -1626,7 +1593,7 @@
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -1935,7 +1902,7 @@
     <col min="3" max="3" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
@@ -2065,7 +2032,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2079,7 +2046,7 @@
     <col min="9" max="9" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>89</v>
       </c>
@@ -2127,8 +2094,9 @@
         <f t="shared" ref="D4:D16" si="0">C4/$C$17</f>
         <v>0.33</v>
       </c>
-      <c r="E4" t="s">
-        <v>101</v>
+      <c r="E4" t="str">
+        <f t="shared" ref="E4:E10" si="1">LOWER(B4)</f>
+        <v>whole grain rolled oats</v>
       </c>
       <c r="G4" s="7">
         <f>ROUND(C4/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2139,16 +2107,16 @@
         <v>14.7651</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4:I16" si="1">RANK(C4,$C$4:$C$16)</f>
+        <f t="shared" ref="I4:I16" si="2">RANK(C4,$C$4:$C$16)</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" t="s">
         <v>102</v>
-      </c>
-      <c r="B5" t="s">
-        <v>103</v>
       </c>
       <c r="C5" s="9">
         <v>17.4</v>
@@ -2157,8 +2125,9 @@
         <f t="shared" si="0"/>
         <v>0.145</v>
       </c>
-      <c r="E5" t="s">
-        <v>104</v>
+      <c r="E5" t="str">
+        <f t="shared" si="1"/>
+        <v>brown rice syrup</v>
       </c>
       <c r="G5" s="7">
         <f>ROUND(C5/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2169,16 +2138,16 @@
         <v>6.4877</v>
       </c>
       <c r="I5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C6" s="9">
         <v>12</v>
@@ -2187,11 +2156,12 @@
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="E6" t="s">
-        <v>107</v>
+      <c r="E6" t="str">
+        <f t="shared" si="1"/>
+        <v>crisp rice</v>
       </c>
       <c r="F6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G6" s="7">
         <f>ROUND(C6/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2202,16 +2172,16 @@
         <v>4.4743</v>
       </c>
       <c r="I6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C7" s="9">
         <v>10.2</v>
@@ -2220,8 +2190,9 @@
         <f t="shared" si="0"/>
         <v>0.085</v>
       </c>
-      <c r="E7" t="s">
-        <v>111</v>
+      <c r="E7" t="str">
+        <f t="shared" si="1"/>
+        <v>clover honey</v>
       </c>
       <c r="G7" s="7">
         <f>ROUND(C7/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2232,16 +2203,16 @@
         <v>3.8031</v>
       </c>
       <c r="I7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C8" s="9">
         <v>9.6</v>
@@ -2250,11 +2221,12 @@
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
-      <c r="E8" t="s">
-        <v>114</v>
+      <c r="E8" t="str">
+        <f t="shared" si="1"/>
+        <v>infused dried cherries</v>
       </c>
       <c r="F8" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G8" s="7">
         <f>ROUND(C8/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2265,16 +2237,16 @@
         <v>3.5794</v>
       </c>
       <c r="I8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C9" s="9">
         <v>8.4</v>
@@ -2283,8 +2255,9 @@
         <f t="shared" si="0"/>
         <v>0.07</v>
       </c>
-      <c r="E9" t="s">
-        <v>118</v>
+      <c r="E9" t="str">
+        <f t="shared" si="1"/>
+        <v>roasted almond butter</v>
       </c>
       <c r="G9" s="7">
         <f>ROUND(C9/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2295,16 +2268,16 @@
         <v>3.132</v>
       </c>
       <c r="I9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C10" s="9">
         <v>7.8</v>
@@ -2313,8 +2286,9 @@
         <f t="shared" si="0"/>
         <v>0.065</v>
       </c>
-      <c r="E10" t="s">
-        <v>121</v>
+      <c r="E10" t="str">
+        <f t="shared" si="1"/>
+        <v>sliced almonds</v>
       </c>
       <c r="G10" s="7">
         <f>ROUND(C10/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2325,16 +2299,16 @@
         <v>2.9083</v>
       </c>
       <c r="I10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C11" s="9">
         <v>6</v>
@@ -2344,7 +2318,7 @@
         <v>0.05</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G11" s="7">
         <f>ROUND(C11/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2355,16 +2329,16 @@
         <v>2.2371</v>
       </c>
       <c r="I11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C12" s="9">
         <v>5.4</v>
@@ -2373,8 +2347,9 @@
         <f t="shared" si="0"/>
         <v>0.045</v>
       </c>
-      <c r="E12" t="s">
-        <v>127</v>
+      <c r="E12" t="str">
+        <f>LOWER(B12)</f>
+        <v>high oleic sunflower oil</v>
       </c>
       <c r="G12" s="7">
         <f>ROUND(C12/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2385,16 +2360,16 @@
         <v>2.0134</v>
       </c>
       <c r="I12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C13" s="9">
         <v>1.56</v>
@@ -2403,8 +2378,9 @@
         <f t="shared" si="0"/>
         <v>0.013</v>
       </c>
-      <c r="E13" t="s">
-        <v>130</v>
+      <c r="E13" t="str">
+        <f>LOWER(B13)</f>
+        <v>vanilla extract</v>
       </c>
       <c r="G13" s="7">
         <f>ROUND(C13/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2415,16 +2391,16 @@
         <v>0.5817</v>
       </c>
       <c r="I13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C14" s="9">
         <v>0.84</v>
@@ -2433,8 +2409,9 @@
         <f t="shared" si="0"/>
         <v>0.007</v>
       </c>
-      <c r="E14" t="s">
-        <v>133</v>
+      <c r="E14" t="str">
+        <f>LOWER(B14)</f>
+        <v>ground cinnamon</v>
       </c>
       <c r="G14" s="7">
         <f>ROUND(C14/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2445,16 +2422,16 @@
         <v>0.3132</v>
       </c>
       <c r="I14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B15" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C15" s="9">
         <v>0.72</v>
@@ -2463,8 +2440,9 @@
         <f t="shared" si="0"/>
         <v>0.006</v>
       </c>
-      <c r="E15" t="s">
-        <v>136</v>
+      <c r="E15" t="str">
+        <f>LOWER(B15)</f>
+        <v>sea salt</v>
       </c>
       <c r="G15" s="7">
         <f>ROUND(C15/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2475,16 +2453,16 @@
         <v>0.2685</v>
       </c>
       <c r="I15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C16" s="9">
         <v>0.48</v>
@@ -2493,8 +2471,9 @@
         <f t="shared" si="0"/>
         <v>0.004</v>
       </c>
-      <c r="E16" t="s">
-        <v>139</v>
+      <c r="E16" t="str">
+        <f>LOWER(B16)</f>
+        <v>soy lecithin</v>
       </c>
       <c r="G16" s="7">
         <f>ROUND(C16/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2505,13 +2484,13 @@
         <v>0.179</v>
       </c>
       <c r="I16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C17" s="9">
         <f>ROUND(SUM(C4:C16),3)</f>
@@ -2528,7 +2507,12 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>141</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2549,9 +2533,9 @@
     <col min="21" max="36" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.2">
@@ -2562,103 +2546,103 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>70</v>
       </c>
       <c r="U3" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="AF3" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="AG3" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="AH3" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="AI3" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="AJ3" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
@@ -2717,7 +2701,7 @@
         <v>362</v>
       </c>
       <c r="S4" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="U4" t="str">
         <f t="shared" ref="U4:U16" si="0">A4</f>
@@ -2786,10 +2770,10 @@
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" t="s">
         <v>102</v>
-      </c>
-      <c r="B5" t="s">
-        <v>103</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -2840,7 +2824,7 @@
         <v>62</v>
       </c>
       <c r="S5" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="0"/>
@@ -2909,10 +2893,10 @@
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -2963,7 +2947,7 @@
         <v>28</v>
       </c>
       <c r="S6" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
@@ -3032,10 +3016,10 @@
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -3086,7 +3070,7 @@
         <v>52</v>
       </c>
       <c r="S7" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="0"/>
@@ -3155,10 +3139,10 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -3209,7 +3193,7 @@
         <v>380</v>
       </c>
       <c r="S8" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="U8" t="str">
         <f t="shared" si="0"/>
@@ -3278,10 +3262,10 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -3332,7 +3316,7 @@
         <v>748</v>
       </c>
       <c r="S9" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="0"/>
@@ -3401,10 +3385,10 @@
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -3455,7 +3439,7 @@
         <v>733</v>
       </c>
       <c r="S10" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="U10" t="str">
         <f t="shared" si="0"/>
@@ -3524,10 +3508,10 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -3578,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="U11" t="str">
         <f t="shared" si="0"/>
@@ -3647,10 +3631,10 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -3701,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="U12" t="str">
         <f t="shared" si="0"/>
@@ -3770,10 +3754,10 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -3824,7 +3808,7 @@
         <v>148</v>
       </c>
       <c r="S13" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="U13" t="str">
         <f t="shared" si="0"/>
@@ -3893,10 +3877,10 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -3947,7 +3931,7 @@
         <v>431</v>
       </c>
       <c r="S14" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="U14" t="str">
         <f t="shared" si="0"/>
@@ -4016,10 +4000,10 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B15" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -4070,7 +4054,7 @@
         <v>8</v>
       </c>
       <c r="S15" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="U15" t="str">
         <f t="shared" si="0"/>
@@ -4139,10 +4123,10 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -4193,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="U16" t="str">
         <f t="shared" si="0"/>
@@ -4262,7 +4246,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -4281,9 +4265,9 @@
     <col min="4" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -4297,49 +4281,49 @@
         <v>96</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
@@ -5306,7 +5290,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C17" s="7">
         <f>ROUND(SUM(C4:C16),4)</f>
@@ -5375,7 +5359,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D18" s="7">
         <f>ROUND(D17*Parameters!$B$4/Parameters!$B$5,4)</f>
@@ -5440,7 +5424,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -5461,9 +5445,9 @@
     <col min="7" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -5474,10 +5458,10 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>3</v>
@@ -5489,7 +5473,7 @@
         <v>5</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -5501,7 +5485,7 @@
         <v>183.6712</v>
       </c>
       <c r="D4" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="E4" s="3">
         <f>IF(C4&lt;5,0,IF(C4&lt;=50,ROUND(C4/5,0)*5,ROUND(C4/10,0)*10))</f>
@@ -5520,7 +5504,7 @@
         <v>6.7614</v>
       </c>
       <c r="D5" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="E5" s="3">
         <f>IF(C5&lt;0.5,0,IF(C5&lt;5,ROUND(C5/0.5,0)*0.5,ROUND(C5,0)))</f>
@@ -5551,7 +5535,7 @@
         <v>0.653</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="E6" s="3">
         <f>IF(C6&lt;0.5,0,IF(C6&lt;5,ROUND(C6/0.5,0)*0.5,ROUND(C6,0)))</f>
@@ -5582,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="E7" s="3">
         <f>IF(C7&lt;0.5,0,IF(C7&lt;5,ROUND(C7/0.5,0)*0.5,ROUND(C7,0)))</f>
@@ -5601,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E8" s="3">
         <f>IF(C8&lt;2,0,IF(C8&lt;=5,"less than 5",ROUND(C8/5,0)*5))</f>
@@ -5632,7 +5616,7 @@
         <v>129.1111</v>
       </c>
       <c r="D9" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E9" s="3">
         <f>IF(C9&lt;5,0,IF(C9&lt;=140,ROUND(C9/5,0)*5,ROUND(C9/10,0)*10))</f>
@@ -5663,7 +5647,7 @@
         <v>27.8143</v>
       </c>
       <c r="D10" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="E10" s="3">
         <f>IF(C10&lt;0.5,0,IF(C10&lt;1,"less than 1",ROUND(C10,0)))</f>
@@ -5694,7 +5678,7 @@
         <v>2.6129</v>
       </c>
       <c r="D11" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="E11" s="3">
         <f>IF(C11&lt;0.5,0,IF(C11&lt;1,"less than 1",ROUND(C11,0)))</f>
@@ -5725,7 +5709,7 @@
         <v>9.4978</v>
       </c>
       <c r="D12" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="E12" s="3">
         <f>IF(C12&lt;0.5,0,IF(C12&lt;1,"less than 1",ROUND(C12,0)))</f>
@@ -5744,7 +5728,7 @@
         <v>7.8514</v>
       </c>
       <c r="D13" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="E13" s="3">
         <f>IF(C13&lt;0.5,0,IF(C13&lt;1,"less than 1",ROUND(C13,0)))</f>
@@ -5775,7 +5759,7 @@
         <v>3.8296</v>
       </c>
       <c r="D14" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="E14" s="3">
         <f>IF(C14&lt;0.5,0,IF(C14&lt;1,"less than 1",ROUND(C14,0)))</f>
@@ -5806,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="E15" s="3">
         <f>IF(C15/F15&lt;0.02,0,ROUND(C15,1))</f>
@@ -5837,7 +5821,7 @@
         <v>33.6223</v>
       </c>
       <c r="D16" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="E16" s="3">
         <f>IF(C16/F16&lt;0.02,0,ROUND(C16/10,0)*10)</f>
@@ -5868,7 +5852,7 @@
         <v>1.0298</v>
       </c>
       <c r="D17" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="E17" s="3">
         <f>IF(C17/F17&lt;0.02,0,ROUND(C17,1))</f>
@@ -5899,7 +5883,7 @@
         <v>130.4153</v>
       </c>
       <c r="D18" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="E18" s="3">
         <f>IF(C18/F18&lt;0.02,0,ROUND(C18/10,0)*10)</f>
@@ -5920,7 +5904,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -5941,9 +5925,9 @@
     <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -5960,10 +5944,10 @@
         <v>95</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -6022,11 +6006,11 @@
       </c>
       <c r="D6" t="str">
         <f>IF(Formula!F6="","",Formula!F6)</f>
-        <v>rice flour, sugar, salt</v>
+        <v>rice, sugar, barley malt extract, salt</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
-        <v>crisp rice (rice flour, sugar, salt)</v>
+        <v>crisp rice (rice, sugar, barley malt extract, salt)</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -6035,7 +6019,7 @@
       </c>
       <c r="B7" t="str">
         <f>Formula!E7</f>
-        <v>honey</v>
+        <v>clover honey</v>
       </c>
       <c r="C7" s="9">
         <f>Formula!C7</f>
@@ -6047,7 +6031,7 @@
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
-        <v>honey</v>
+        <v>clover honey</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -6056,7 +6040,7 @@
       </c>
       <c r="B8" t="str">
         <f>Formula!E8</f>
-        <v>dried cherries</v>
+        <v>infused dried cherries</v>
       </c>
       <c r="C8" s="9">
         <f>Formula!C8</f>
@@ -6064,11 +6048,11 @@
       </c>
       <c r="D8" t="str">
         <f>IF(Formula!F8="","",Formula!F8)</f>
-        <v>cherries, sugar, sunflower oil</v>
+        <v>tart cherries, sugar, sunflower oil</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
-        <v>dried cherries (cherries, sugar, sunflower oil)</v>
+        <v>infused dried cherries (tart cherries, sugar, sunflower oil)</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -6077,7 +6061,7 @@
       </c>
       <c r="B9" t="str">
         <f>Formula!E9</f>
-        <v>almond butter</v>
+        <v>roasted almond butter</v>
       </c>
       <c r="C9" s="9">
         <f>Formula!C9</f>
@@ -6089,10 +6073,10 @@
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
-        <v>almond butter</v>
+        <v>roasted almond butter</v>
       </c>
       <c r="F9" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -6116,7 +6100,7 @@
         <v>sliced almonds</v>
       </c>
       <c r="F10" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -6125,7 +6109,7 @@
       </c>
       <c r="B11" t="str">
         <f>Formula!E12</f>
-        <v>sunflower oil</v>
+        <v>high oleic sunflower oil</v>
       </c>
       <c r="C11" s="9">
         <f>Formula!C12</f>
@@ -6137,7 +6121,7 @@
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
-        <v>sunflower oil</v>
+        <v>high oleic sunflower oil</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -6146,7 +6130,7 @@
       </c>
       <c r="B12" t="str">
         <f>Formula!E13</f>
-        <v>natural vanilla flavor</v>
+        <v>vanilla extract</v>
       </c>
       <c r="C12" s="9">
         <f>Formula!C13</f>
@@ -6158,7 +6142,7 @@
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
-        <v>natural vanilla flavor</v>
+        <v>vanilla extract</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -6167,7 +6151,7 @@
       </c>
       <c r="B13" t="str">
         <f>Formula!E14</f>
-        <v>cinnamon</v>
+        <v>ground cinnamon</v>
       </c>
       <c r="C13" s="9">
         <f>Formula!C14</f>
@@ -6179,7 +6163,7 @@
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
-        <v>cinnamon</v>
+        <v>ground cinnamon</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -6224,21 +6208,21 @@
         <v>soy lecithin</v>
       </c>
       <c r="F15" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B17" t="str">
         <f>UPPER(LEFT(E4&amp;", "&amp;E5&amp;", "&amp;E6&amp;", "&amp;E7&amp;", "&amp;E8&amp;", "&amp;E9&amp;", "&amp;E10&amp;", "&amp;E11&amp;", "&amp;E12&amp;", "&amp;E13&amp;", "&amp;E14&amp;", "&amp;E15,1))&amp;MID(E4&amp;", "&amp;E5&amp;", "&amp;E6&amp;", "&amp;E7&amp;", "&amp;E8&amp;", "&amp;E9&amp;", "&amp;E10&amp;", "&amp;E11&amp;", "&amp;E12&amp;", "&amp;E13&amp;", "&amp;E14&amp;", "&amp;E15,2,900)&amp;"."</f>
-        <v>Whole grain rolled oats, brown rice syrup, crisp rice (rice flour, sugar, salt), honey, dried cherries (cherries, sugar, sunflower oil), almond butter, sliced almonds, sunflower oil, natural vanilla flavor, cinnamon, sea salt, soy lecithin.</v>
+        <v>Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract, ground cinnamon, sea salt, soy lecithin.</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B18" t="str">
         <f>"Contains: "&amp;IF(COUNTIF(F4:F15,"almonds")&gt;0,"almonds","")&amp;IF(COUNTIF(F4:F15,"soy")&gt;0,", soy","")&amp;"."</f>
@@ -6247,7 +6231,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="B19">
         <f>COUNTA(B4:B15)</f>
@@ -6256,7 +6240,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -6278,45 +6262,45 @@
     <col min="7" max="7" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C4" s="12">
         <f>Parameters!$B$11*100</f>
@@ -6335,15 +6319,15 @@
         <v>Not supported</v>
       </c>
       <c r="G4" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="B5" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C5" s="12">
         <f>Parameters!$B$13</f>
@@ -6367,10 +6351,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="B6" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="C6" s="8">
         <f>Parameters!$B$14</f>
@@ -6386,30 +6370,30 @@
         <v>Supported</v>
       </c>
       <c r="G6" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B7" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="F7" t="str">
         <f>IF(COUNTIF(Formula!B4:B16,"*artificial*")=0,"Supported","Not supported")</f>
         <v>Supported</v>
       </c>
       <c r="G7" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -6422,15 +6406,15 @@
         <v>Not supported</v>
       </c>
       <c r="G8" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="B9" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -6443,12 +6427,12 @@
         <v>Supported</v>
       </c>
       <c r="G9" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="B11">
         <f>COUNTIF(F4:F9,"Supported")</f>
@@ -6466,7 +6450,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/submissions/08-nutrition-panel-granola/solution/oat_cherry_bar_label_review.xlsx
+++ b/submissions/08-nutrition-panel-granola/solution/oat_cherry_bar_label_review.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A199CD1A-C115-4D41-B8C7-F67E77C33416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AE37E7-603D-694E-951D-6728693D360A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Panel" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="242">
   <si>
     <t>Nutrition Facts, Oat and Cherry Bar, formula OCB-26-03, as the wrapper will print</t>
   </si>
@@ -432,7 +432,7 @@
     <t>DECLARED_NAME is the common name on the formula in lower case under SOP 4.1; SUB_INGREDIENTS are typed from specification S-1187 revision 7 for the crisp rice and specification S-3301 revision 5 for the cherries, in the order each lists them.</t>
   </si>
   <si>
-    <t>Supplier nutrient specifications, ingredient_nutrient_specs.csv, and the same values normalised to 100 g per SOP 1.2</t>
+    <t>Supplier nutrient specifications from ingredient_nutrient_specs.csv and the specifications in force, and the same values normalised to 100 g per SOP 1.2</t>
   </si>
   <si>
     <t>BASIS_G</t>
@@ -537,7 +537,7 @@
     <t>Supplier spec S-2210 rev 2</t>
   </si>
   <si>
-    <t>Supplier spec S-1187 rev 7 per 30 g serving</t>
+    <t>Supplier spec S-1187 rev 7</t>
   </si>
   <si>
     <t>Supplier spec S-2205 rev 3</t>
@@ -570,7 +570,10 @@
     <t>Supplier spec S-5055 rev 4</t>
   </si>
   <si>
-    <t>BASIS_G is the weight each specification states its values on; the crisp rice specification S-1187 is stated per 30 g serving and is converted to 100 g in the right-hand block before use.</t>
+    <t>BASIS_G is the weight each specification states its values on. The nutrient sheet marks the crisp rice and the almond butter as stated per serving; specification S-1187 is stated per 30 g serving and specification S-3120 per 32 g serving, and both are converted to 100 g in the right-hand block before use.</t>
+  </si>
+  <si>
+    <t>The cherries row carries specification S-3301 revision 5, the specification in force, in place of the revision 4 row on the nutrient sheet, which states total sugars at 58.0 g and no added sugars figure.</t>
   </si>
   <si>
     <t>Nutrient contribution of each ingredient to one serving, grams in the serving times the per-100 g specification over 100</t>
@@ -648,7 +651,7 @@
     <t>Ingredients declared</t>
   </si>
   <si>
-    <t>Water is left off under SOP 4.1 because it is removed in the bake. The almonds are named as the specific tree nut under 4.2, and the soy lecithin carries the soy declaration. The barley malt extract in the crisp rice is a gluten source and not a major food allergen, and specification S-1187 states that none is present in the product, so the Contains statement stays at almonds and soy.</t>
+    <t>Water is left off under SOP 4.1 because it is removed in the bake. The almonds are named as the specific tree nut under 4.2, and the soy lecithin carries the soy declaration. The barley malt extract in the crisp rice is a gluten source and not a major food allergen, and specification S-1187 states that none is present in the product, so the Contains statement stays at almonds and soy. Specification S-3120 states the almond butter as dry roasted almonds alone, so it prints as a single ingredient.</t>
   </si>
   <si>
     <t>Each claim in the product brief tested under SOP QA-14 section 5 on the unrounded amount per reference amount and per serving</t>
@@ -693,6 +696,9 @@
     <t>Sodium in mg, both bases at or below the ceiling</t>
   </si>
   <si>
+    <t>SOP 5.1 and 5.2; the bar clears the ceiling per reference amount and exceeds it per serving, and both must pass</t>
+  </si>
+  <si>
     <t>Made with whole grain oats</t>
   </si>
   <si>
@@ -741,33 +747,34 @@
     <t>Priya, this is the label review for the Oat and Cherry Bar, formula OCB-26-03. The panel on the first tab is what prints, and every declared value on it reads from the Rounding tab, which reads from the Nutrients tab, which reads from the Formula and Specs tabs; nothing on the panel is typed in. The serving is one bar at the 42 gram target net weight under SOP QA-14 section 1.3, not the 42.1 gram pilot average, and one bar is one serving because 42 grams sits between 67 and 200 percent of the 40 gram reference amount.</t>
   </si>
   <si>
-    <t>Two things in the inputs change the numbers and are worth knowing before legal asks. The crisp rice specification S-1187 states its values per 30 g serving, not per 100 g, so the Specs tab converts it before use; taken as per 100 g it would understate sodium and sugars from that ingredient by more than two thirds. The pilot batch lost 12.72 kg in the bake, so every nutrient is carried into a finished batch weight of 107.28 kg at a yield of 0.8940. A bar at 42 grams carries the nutrients of 46.98 grams of formula.</t>
-  </si>
-  <si>
-    <t>The cherries drive the added sugars line. Specification S-3301 revision 5 puts 30.0 g of the 60.0 g of sugars per 100 g as added, the sucrose taken up in the infusion, and revision 5 is the specification in force for every lot we hold, so the panel uses it. With the brown rice syrup and honey the bar carries 7.851 g of added sugars unrounded, declared as 8 g at 16 percent of the daily value, against 9.498 g of total sugars declared as 9 g. The percent daily values are computed from the declared, rounded amount under section 3.1, which is why the added sugars line shows 16 percent and not 15.7.</t>
+    <t>Two things in the inputs change the numbers beyond the cherries below, and they are worth knowing before legal asks. The nutrient sheet marks the crisp rice and the almond butter as stated per serving and gives no serving weight. Specification S-1187 states the crisp rice per 30 g serving, and specification S-3120 states the almond butter per 32 g serving. The Specs tab converts both to 100 g before use; taken as per 100 g they would understate the sodium from the crisp rice and the fat from the almond butter by more than two thirds. The pilot batch lost 12.72 kg in the bake, so every nutrient is carried into a finished batch weight of 107.28 kg at a yield of 0.8940. A bar at 42 grams carries the nutrients of 46.98 grams of formula.</t>
+  </si>
+  <si>
+    <t>The cherries drive the added sugars line, and the nutrient sheet is out of date on them. Its cherries row is still specification S-3301 revision 4, with total sugars at 58.0 g per 100 g and no added sugars figure. Revision 5 is the specification in force for every lot we hold, so the panel uses it under section 1.2. Revision 5 puts 30.0 g of the 60.0 g of sugars per 100 g as added, the sucrose taken up in the infusion. With the brown rice syrup and honey the bar carries 7.851 g of added sugars unrounded, declared as 8 g at 16 percent of the daily value, against 9.497 g of total sugars declared as 9 g. Taken from the nutrient sheet row, the added sugars line would print 7 g. The percent daily values are computed from the declared, rounded amount under section 3.1, which is why the added sugars line shows 16 percent and not 15.7.</t>
   </si>
   <si>
     <t>The ingredient statement lists twelve ingredients in descending order of formula weight with water left off under section 4.1, each under its common name on the formula, and it reads: Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract, ground cinnamon, sea salt, soy lecithin. The two compound ingredients carry the sub-ingredients their specifications list, S-1187 revision 7 for the crisp rice and S-3301 revision 5 for the cherries. The Contains statement reads Contains almonds and soy; the barley malt extract in the crisp rice is a gluten source and not a major food allergen, and S-1187 states that none is present in the product.</t>
   </si>
   <si>
-    <t>On the claims. Good source of fiber is not supported. The panel declares 3 g of fiber at 11 percent of the daily value, because the declared value rounds up from 2.613 g, but section 5.1 tests the claim on the unrounded amount per reference amount and per serving, and the bar carries 2.489 g per 40 g reference amount, which is 8.9 percent of the daily value, and 9.3 percent per 42 gram serving. Both fall short of 10 percent, so the claim cannot go on the wrapper as the formula stands. It would take 2.8 g of fiber per 40 g to clear. Low sodium is supported at 123 mg per reference amount and 129.1 mg per serving against the 140 mg ceiling.</t>
+    <t>On the claims. Good source of fiber is not supported. The panel declares 3 g of fiber at 11 percent of the daily value, because the declared value rounds up from 2.613 g, but section 5.1 tests the claim on the unrounded amount per reference amount and per serving. The bar carries 2.489 g per 40 g reference amount, which is 8.9 percent of the daily value, and 9.3 percent per 42 gram serving. Both fall short of 10 percent, so the claim cannot go on the wrapper as the formula stands. Low sodium is not supported either. The bar carries 135.9 mg per 40 g reference amount, which clears the 140 mg ceiling. It carries 142.7 mg per 42 gram serving, which does not, and section 5.1 requires both bases to pass. The panel prints 140 mg because section 2.4 rounds to the nearest 10 above 140, so the wrapper would show the ceiling figure beside a claim the bar does not meet.</t>
   </si>
   <si>
     <t>Made with whole grain oats is supported as a company statement under section 5.3: the bar carries 15.50 g of whole grain rolled oats per serving against the 8 gram floor. No artificial flavors is supported; the only flavorings in the formula are the vanilla extract, which specification S-5020 states as a natural extract, and the barley malt extract inside the crisp rice, which S-1187 states is its only flavoring. Real fruit is supported on the dried tart cherries, 3.76 g per bar. No added sugar is not supported and cannot be: the formula adds brown rice syrup, honey, sugar-infused cherries and a crisp rice that carries sugar of its own, and the panel declares 8 g of added sugars, so section 5.2 rules the flag out however it is worded.</t>
   </si>
   <si>
-    <t>Things for you to decide or take to a supplier before the copy locks. First, the fiber claim comes off the front panel unless product development reopens the frozen formula; the nearest lift is the oats, and that is a formula change, not a wording change. Second, the no added sugar flag comes off; the sales lead should hear the 8 g figure rather than a softer claim. Third, the Contains statement rests on the formula and the two specifications, and neither wheat nor barley belongs in it. S-1187 says the crisp rice packing line also runs a wheat flake cereal with a swab between runs, and the file carries no statement of what else runs on our co-packer line. QA should decide whether a shared-line advisory prints under the Contains statement before the wrapper goes. The workbook cites every specification revision it used on the Specs tab.</t>
+    <t>Things for you to decide or take to a supplier before the copy locks. First, the fiber claim comes off the front panel unless product development reopens the frozen formula; the nearest lift is the oats, and that is a formula change, not a wording change. Second, the no added sugar flag comes off; the sales lead should hear the 8 g figure rather than a softer claim. Third, the low sodium flag comes off as the formula stands. Cutting the sea salt from 0.81 kg to 0.79 kg per batch would bring the serving to 139.7 mg, and that is also a formula change. Fourth, purchasing should reissue the nutrient sheet with the cherries at revision 5 and with the serving weights beside the two per serving rows. Fifth, the Contains statement rests on the formula and the three specifications, and wheat, barley and peanuts do not belong in it. S-1187 says the crisp rice packing line also runs a wheat flake cereal, and S-3120 says the almond butter line runs peanut butter on alternate weeks. QA should decide whether a shared-line advisory prints under the Contains statement before the wrapper goes. The workbook cites every specification revision it used on the Specs tab.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.00000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -830,13 +837,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1292,7 +1299,7 @@
       </c>
       <c r="B12" s="3">
         <f>Rounding!E9</f>
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
@@ -1502,7 +1509,7 @@
       </c>
       <c r="B24">
         <f>Claims!B11</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" t="s">
         <v>35</v>
@@ -1514,7 +1521,7 @@
       </c>
       <c r="B25">
         <f>Claims!B12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="s">
         <v>35</v>
@@ -1540,42 +1547,42 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
-        <v>233</v>
+      <c r="A3" s="13" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
-        <v>234</v>
+      <c r="A4" s="13" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
-        <v>235</v>
+      <c r="A5" s="13" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
-        <v>236</v>
+      <c r="A6" s="13" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
-        <v>237</v>
+      <c r="A7" s="13" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
-        <v>238</v>
+      <c r="A8" s="13" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
-        <v>239</v>
+      <c r="A9" s="13" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -2090,8 +2097,8 @@
       <c r="C4" s="9">
         <v>39.6</v>
       </c>
-      <c r="D4" s="10">
-        <f t="shared" ref="D4:D16" si="0">C4/$C$17</f>
+      <c r="D4" s="14">
+        <f t="shared" ref="D4:D16" si="0">ROUND(C4/$C$17,5)</f>
         <v>0.33</v>
       </c>
       <c r="E4" t="str">
@@ -2121,7 +2128,7 @@
       <c r="C5" s="9">
         <v>17.4</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="14">
         <f t="shared" si="0"/>
         <v>0.145</v>
       </c>
@@ -2152,7 +2159,7 @@
       <c r="C6" s="9">
         <v>12</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="14">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
@@ -2186,7 +2193,7 @@
       <c r="C7" s="9">
         <v>10.2</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="14">
         <f t="shared" si="0"/>
         <v>0.085</v>
       </c>
@@ -2217,7 +2224,7 @@
       <c r="C8" s="9">
         <v>9.6</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="14">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
@@ -2251,7 +2258,7 @@
       <c r="C9" s="9">
         <v>8.4</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="14">
         <f t="shared" si="0"/>
         <v>0.07</v>
       </c>
@@ -2282,7 +2289,7 @@
       <c r="C10" s="9">
         <v>7.8</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="14">
         <f t="shared" si="0"/>
         <v>0.065</v>
       </c>
@@ -2311,22 +2318,22 @@
         <v>116</v>
       </c>
       <c r="C11" s="9">
-        <v>6</v>
-      </c>
-      <c r="D11" s="10">
+        <v>5.91</v>
+      </c>
+      <c r="D11" s="14">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.04925</v>
       </c>
       <c r="E11" t="s">
         <v>117</v>
       </c>
       <c r="G11" s="7">
         <f>ROUND(C11/Parameters!$B$7*Parameters!$B$5,4)</f>
-        <v>2.349</v>
+        <v>2.3138</v>
       </c>
       <c r="H11" s="7">
         <f>ROUND(C11/Parameters!$B$7*Parameters!$B$4,4)</f>
-        <v>2.2371</v>
+        <v>2.2036</v>
       </c>
       <c r="I11">
         <f t="shared" si="2"/>
@@ -2343,7 +2350,7 @@
       <c r="C12" s="9">
         <v>5.4</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="14">
         <f t="shared" si="0"/>
         <v>0.045</v>
       </c>
@@ -2374,7 +2381,7 @@
       <c r="C13" s="9">
         <v>1.56</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="14">
         <f t="shared" si="0"/>
         <v>0.013</v>
       </c>
@@ -2405,7 +2412,7 @@
       <c r="C14" s="9">
         <v>0.84</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="14">
         <f t="shared" si="0"/>
         <v>0.007</v>
       </c>
@@ -2434,11 +2441,11 @@
         <v>125</v>
       </c>
       <c r="C15" s="9">
-        <v>0.72</v>
-      </c>
-      <c r="D15" s="10">
+        <v>0.81</v>
+      </c>
+      <c r="D15" s="14">
         <f t="shared" si="0"/>
-        <v>0.006</v>
+        <v>0.00675</v>
       </c>
       <c r="E15" t="str">
         <f>LOWER(B15)</f>
@@ -2446,11 +2453,11 @@
       </c>
       <c r="G15" s="7">
         <f>ROUND(C15/Parameters!$B$7*Parameters!$B$5,4)</f>
-        <v>0.2819</v>
+        <v>0.3171</v>
       </c>
       <c r="H15" s="7">
         <f>ROUND(C15/Parameters!$B$7*Parameters!$B$4,4)</f>
-        <v>0.2685</v>
+        <v>0.302</v>
       </c>
       <c r="I15">
         <f t="shared" si="2"/>
@@ -2467,7 +2474,7 @@
       <c r="C16" s="9">
         <v>0.48</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="14">
         <f t="shared" si="0"/>
         <v>0.004</v>
       </c>
@@ -2522,7 +2529,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AJ18"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3268,16 +3275,16 @@
         <v>112</v>
       </c>
       <c r="C9">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>614</v>
+        <v>196</v>
       </c>
       <c r="E9">
-        <v>55.5</v>
+        <v>17.8</v>
       </c>
       <c r="F9">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3286,34 +3293,34 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J9">
-        <v>18.8</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>10.3</v>
+        <v>3.3</v>
       </c>
       <c r="L9">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>21</v>
+        <v>6.7</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>347</v>
+        <v>111</v>
       </c>
       <c r="Q9">
-        <v>3.49</v>
+        <v>1.12</v>
       </c>
       <c r="R9">
-        <v>748</v>
+        <v>239</v>
       </c>
       <c r="S9" t="s">
         <v>169</v>
@@ -3324,15 +3331,15 @@
       </c>
       <c r="V9" s="7">
         <f t="shared" si="1"/>
-        <v>614</v>
+        <v>612.5</v>
       </c>
       <c r="W9" s="7">
         <f t="shared" si="2"/>
-        <v>55.5</v>
+        <v>55.625</v>
       </c>
       <c r="X9" s="7">
         <f t="shared" si="3"/>
-        <v>4.2</v>
+        <v>4.0625</v>
       </c>
       <c r="Y9" s="7">
         <f t="shared" si="4"/>
@@ -3344,19 +3351,19 @@
       </c>
       <c r="AA9" s="7">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AB9" s="7">
         <f t="shared" si="7"/>
-        <v>18.8</v>
+        <v>18.75</v>
       </c>
       <c r="AC9" s="7">
         <f t="shared" si="8"/>
-        <v>10.3</v>
+        <v>10.3125</v>
       </c>
       <c r="AD9" s="7">
         <f t="shared" si="9"/>
-        <v>4.4</v>
+        <v>4.375</v>
       </c>
       <c r="AE9" s="7">
         <f t="shared" si="10"/>
@@ -3364,7 +3371,7 @@
       </c>
       <c r="AF9" s="7">
         <f t="shared" si="11"/>
-        <v>21</v>
+        <v>20.9375</v>
       </c>
       <c r="AG9" s="7">
         <f t="shared" si="12"/>
@@ -3372,15 +3379,15 @@
       </c>
       <c r="AH9" s="7">
         <f t="shared" si="13"/>
-        <v>347</v>
+        <v>346.875</v>
       </c>
       <c r="AI9" s="7">
         <f t="shared" si="14"/>
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="AJ9" s="7">
         <f t="shared" si="15"/>
-        <v>748</v>
+        <v>746.875</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.2">
@@ -4247,6 +4254,11 @@
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -4267,7 +4279,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -4711,15 +4723,15 @@
       </c>
       <c r="D9" s="7">
         <f>ROUND($C9/100*Specs!V9,4)</f>
-        <v>20.192</v>
+        <v>20.1427</v>
       </c>
       <c r="E9" s="7">
         <f>ROUND($C9/100*Specs!W9,4)</f>
-        <v>1.8252</v>
+        <v>1.8293</v>
       </c>
       <c r="F9" s="7">
         <f>ROUND($C9/100*Specs!X9,4)</f>
-        <v>0.1381</v>
+        <v>0.1336</v>
       </c>
       <c r="G9" s="7">
         <f>ROUND($C9/100*Specs!Y9,4)</f>
@@ -4731,19 +4743,19 @@
       </c>
       <c r="I9" s="7">
         <f>ROUND($C9/100*Specs!AA9,4)</f>
-        <v>0.2302</v>
+        <v>0.2055</v>
       </c>
       <c r="J9" s="7">
         <f>ROUND($C9/100*Specs!AB9,4)</f>
-        <v>0.6183</v>
+        <v>0.6166</v>
       </c>
       <c r="K9" s="7">
         <f>ROUND($C9/100*Specs!AC9,4)</f>
-        <v>0.3387</v>
+        <v>0.3391</v>
       </c>
       <c r="L9" s="7">
         <f>ROUND($C9/100*Specs!AD9,4)</f>
-        <v>0.1447</v>
+        <v>0.1439</v>
       </c>
       <c r="M9" s="7">
         <f>ROUND($C9/100*Specs!AE9,4)</f>
@@ -4751,7 +4763,7 @@
       </c>
       <c r="N9" s="7">
         <f>ROUND($C9/100*Specs!AF9,4)</f>
-        <v>0.6906</v>
+        <v>0.6886</v>
       </c>
       <c r="O9" s="7">
         <f>ROUND($C9/100*Specs!AG9,4)</f>
@@ -4759,15 +4771,15 @@
       </c>
       <c r="P9" s="7">
         <f>ROUND($C9/100*Specs!AH9,4)</f>
-        <v>11.4114</v>
+        <v>11.4073</v>
       </c>
       <c r="Q9" s="7">
         <f>ROUND($C9/100*Specs!AI9,4)</f>
-        <v>0.1148</v>
+        <v>0.1151</v>
       </c>
       <c r="R9" s="7">
         <f>ROUND($C9/100*Specs!AJ9,4)</f>
-        <v>24.5987</v>
+        <v>24.5617</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
@@ -4855,7 +4867,7 @@
       </c>
       <c r="C11" s="7">
         <f>Formula!G11</f>
-        <v>2.349</v>
+        <v>2.3138</v>
       </c>
       <c r="D11" s="7">
         <f>ROUND($C11/100*Specs!V11,4)</f>
@@ -5151,7 +5163,7 @@
       </c>
       <c r="C15" s="7">
         <f>Formula!G15</f>
-        <v>0.2819</v>
+        <v>0.3171</v>
       </c>
       <c r="D15" s="7">
         <f>ROUND($C15/100*Specs!V15,4)</f>
@@ -5175,7 +5187,7 @@
       </c>
       <c r="I15" s="7">
         <f>ROUND($C15/100*Specs!AA15,4)</f>
-        <v>109.2588</v>
+        <v>122.9016</v>
       </c>
       <c r="J15" s="7">
         <f>ROUND($C15/100*Specs!AB15,4)</f>
@@ -5203,15 +5215,15 @@
       </c>
       <c r="P15" s="7">
         <f>ROUND($C15/100*Specs!AH15,4)</f>
-        <v>0.0677</v>
+        <v>0.0761</v>
       </c>
       <c r="Q15" s="7">
         <f>ROUND($C15/100*Specs!AI15,4)</f>
-        <v>0.0009</v>
+        <v>1E-3</v>
       </c>
       <c r="R15" s="7">
         <f>ROUND($C15/100*Specs!AJ15,4)</f>
-        <v>0.0226</v>
+        <v>0.0254</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -5290,7 +5302,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C17" s="7">
         <f>ROUND(SUM(C4:C16),4)</f>
@@ -5298,15 +5310,15 @@
       </c>
       <c r="D17" s="7">
         <f t="shared" ref="D17:R17" si="0">SUM(D4:D16)</f>
-        <v>183.6712</v>
+        <v>183.6219</v>
       </c>
       <c r="E17" s="7">
         <f t="shared" si="0"/>
-        <v>6.7614</v>
+        <v>6.7655</v>
       </c>
       <c r="F17" s="7">
         <f t="shared" si="0"/>
-        <v>0.653</v>
+        <v>0.6485</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" si="0"/>
@@ -5318,19 +5330,19 @@
       </c>
       <c r="I17" s="7">
         <f t="shared" si="0"/>
-        <v>129.1111</v>
+        <v>142.7292</v>
       </c>
       <c r="J17" s="7">
         <f t="shared" si="0"/>
-        <v>27.8143</v>
+        <v>27.8126</v>
       </c>
       <c r="K17" s="7">
         <f t="shared" si="0"/>
-        <v>2.6129</v>
+        <v>2.6133</v>
       </c>
       <c r="L17" s="7">
         <f t="shared" si="0"/>
-        <v>9.4978</v>
+        <v>9.497</v>
       </c>
       <c r="M17" s="7">
         <f t="shared" si="0"/>
@@ -5338,7 +5350,7 @@
       </c>
       <c r="N17" s="7">
         <f t="shared" si="0"/>
-        <v>3.8296</v>
+        <v>3.8276</v>
       </c>
       <c r="O17" s="7">
         <f t="shared" si="0"/>
@@ -5346,32 +5358,32 @@
       </c>
       <c r="P17" s="7">
         <f t="shared" si="0"/>
-        <v>33.6223</v>
+        <v>33.6266</v>
       </c>
       <c r="Q17" s="7">
         <f t="shared" si="0"/>
-        <v>1.0298</v>
+        <v>1.0302</v>
       </c>
       <c r="R17" s="7">
         <f t="shared" si="0"/>
-        <v>130.4153</v>
+        <v>130.3811</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D18" s="7">
         <f>ROUND(D17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>174.925</v>
+        <v>174.878</v>
       </c>
       <c r="E18" s="7">
         <f>ROUND(E17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>6.4394</v>
+        <v>6.4433</v>
       </c>
       <c r="F18" s="7">
         <f>ROUND(F17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>0.6219</v>
+        <v>0.6176</v>
       </c>
       <c r="G18" s="7">
         <f>ROUND(G17*Parameters!$B$4/Parameters!$B$5,4)</f>
@@ -5383,19 +5395,19 @@
       </c>
       <c r="I18" s="7">
         <f>ROUND(I17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>122.963</v>
+        <v>135.9326</v>
       </c>
       <c r="J18" s="7">
         <f>ROUND(J17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>26.4898</v>
+        <v>26.4882</v>
       </c>
       <c r="K18" s="7">
         <f>ROUND(K17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>2.4885</v>
+        <v>2.4889</v>
       </c>
       <c r="L18" s="7">
         <f>ROUND(L17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>9.0455</v>
+        <v>9.0448</v>
       </c>
       <c r="M18" s="7">
         <f>ROUND(M17*Parameters!$B$4/Parameters!$B$5,4)</f>
@@ -5403,7 +5415,7 @@
       </c>
       <c r="N18" s="7">
         <f>ROUND(N17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>3.6472</v>
+        <v>3.6453</v>
       </c>
       <c r="O18" s="7">
         <f>ROUND(O17*Parameters!$B$4/Parameters!$B$5,4)</f>
@@ -5411,20 +5423,20 @@
       </c>
       <c r="P18" s="7">
         <f>ROUND(P17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>32.0212</v>
+        <v>32.0253</v>
       </c>
       <c r="Q18" s="7">
         <f>ROUND(Q17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>0.9808</v>
+        <v>0.9811</v>
       </c>
       <c r="R18" s="7">
         <f>ROUND(R17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>124.205</v>
+        <v>124.1725</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -5447,7 +5459,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -5458,10 +5470,10 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>3</v>
@@ -5473,7 +5485,7 @@
         <v>5</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -5482,10 +5494,10 @@
       </c>
       <c r="C4" s="7">
         <f>Nutrients!D17</f>
-        <v>183.6712</v>
+        <v>183.6219</v>
       </c>
       <c r="D4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E4" s="3">
         <f>IF(C4&lt;5,0,IF(C4&lt;=50,ROUND(C4/5,0)*5,ROUND(C4/10,0)*10))</f>
@@ -5501,10 +5513,10 @@
       </c>
       <c r="C5" s="7">
         <f>Nutrients!E17</f>
-        <v>6.7614</v>
+        <v>6.7655</v>
       </c>
       <c r="D5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E5" s="3">
         <f>IF(C5&lt;0.5,0,IF(C5&lt;5,ROUND(C5/0.5,0)*0.5,ROUND(C5,0)))</f>
@@ -5518,7 +5530,7 @@
         <f>IF(ISNUMBER(E5),ROUND(E5/F5,2),ROUND(C5/F5,2))</f>
         <v>0.09</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="10">
         <f>ROUND(C5/F5,3)</f>
         <v>0.087</v>
       </c>
@@ -5532,10 +5544,10 @@
       </c>
       <c r="C6" s="7">
         <f>Nutrients!F17</f>
-        <v>0.653</v>
+        <v>0.6485</v>
       </c>
       <c r="D6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E6" s="3">
         <f>IF(C6&lt;0.5,0,IF(C6&lt;5,ROUND(C6/0.5,0)*0.5,ROUND(C6,0)))</f>
@@ -5549,9 +5561,9 @@
         <f>IF(ISNUMBER(E6),ROUND(E6/F6,2),ROUND(C6/F6,2))</f>
         <v>0.03</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="10">
         <f>ROUND(C6/F6,3)</f>
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -5566,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E7" s="3">
         <f>IF(C7&lt;0.5,0,IF(C7&lt;5,ROUND(C7/0.5,0)*0.5,ROUND(C7,0)))</f>
@@ -5585,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E8" s="3">
         <f>IF(C8&lt;2,0,IF(C8&lt;=5,"less than 5",ROUND(C8/5,0)*5))</f>
@@ -5599,7 +5611,7 @@
         <f>IF(ISNUMBER(E8),ROUND(E8/F8,2),ROUND(C8/F8,2))</f>
         <v>0</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="10">
         <f>ROUND(C8/F8,3)</f>
         <v>0</v>
       </c>
@@ -5613,14 +5625,14 @@
       </c>
       <c r="C9" s="7">
         <f>Nutrients!I17</f>
-        <v>129.1111</v>
+        <v>142.7292</v>
       </c>
       <c r="D9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E9" s="3">
         <f>IF(C9&lt;5,0,IF(C9&lt;=140,ROUND(C9/5,0)*5,ROUND(C9/10,0)*10))</f>
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F9">
         <f>Parameters!B20</f>
@@ -5630,9 +5642,9 @@
         <f>IF(ISNUMBER(E9),ROUND(E9/F9,2),ROUND(C9/F9,2))</f>
         <v>0.06</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="10">
         <f>ROUND(C9/F9,3)</f>
-        <v>0.056</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -5644,10 +5656,10 @@
       </c>
       <c r="C10" s="7">
         <f>Nutrients!J17</f>
-        <v>27.8143</v>
+        <v>27.8126</v>
       </c>
       <c r="D10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E10" s="3">
         <f>IF(C10&lt;0.5,0,IF(C10&lt;1,"less than 1",ROUND(C10,0)))</f>
@@ -5661,7 +5673,7 @@
         <f>IF(ISNUMBER(E10),ROUND(E10/F10,2),ROUND(C10/F10,2))</f>
         <v>0.1</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="10">
         <f>ROUND(C10/F10,3)</f>
         <v>0.101</v>
       </c>
@@ -5675,10 +5687,10 @@
       </c>
       <c r="C11" s="7">
         <f>Nutrients!K17</f>
-        <v>2.6129</v>
+        <v>2.6133</v>
       </c>
       <c r="D11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E11" s="3">
         <f>IF(C11&lt;0.5,0,IF(C11&lt;1,"less than 1",ROUND(C11,0)))</f>
@@ -5692,7 +5704,7 @@
         <f>IF(ISNUMBER(E11),ROUND(E11/F11,2),ROUND(C11/F11,2))</f>
         <v>0.11</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="10">
         <f>ROUND(C11/F11,3)</f>
         <v>0.093</v>
       </c>
@@ -5706,10 +5718,10 @@
       </c>
       <c r="C12" s="7">
         <f>Nutrients!L17</f>
-        <v>9.4978</v>
+        <v>9.497</v>
       </c>
       <c r="D12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E12" s="3">
         <f>IF(C12&lt;0.5,0,IF(C12&lt;1,"less than 1",ROUND(C12,0)))</f>
@@ -5728,7 +5740,7 @@
         <v>7.8514</v>
       </c>
       <c r="D13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E13" s="3">
         <f>IF(C13&lt;0.5,0,IF(C13&lt;1,"less than 1",ROUND(C13,0)))</f>
@@ -5742,7 +5754,7 @@
         <f t="shared" ref="G13:G18" si="0">IF(ISNUMBER(E13),ROUND(E13/F13,2),ROUND(C13/F13,2))</f>
         <v>0.16</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="10">
         <f t="shared" ref="H13:H18" si="1">ROUND(C13/F13,3)</f>
         <v>0.157</v>
       </c>
@@ -5756,10 +5768,10 @@
       </c>
       <c r="C14" s="7">
         <f>Nutrients!N17</f>
-        <v>3.8296</v>
+        <v>3.8276</v>
       </c>
       <c r="D14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E14" s="3">
         <f>IF(C14&lt;0.5,0,IF(C14&lt;1,"less than 1",ROUND(C14,0)))</f>
@@ -5773,7 +5785,7 @@
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="10">
         <f t="shared" si="1"/>
         <v>0.077</v>
       </c>
@@ -5790,7 +5802,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E15" s="3">
         <f>IF(C15/F15&lt;0.02,0,ROUND(C15,1))</f>
@@ -5804,7 +5816,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5818,10 +5830,10 @@
       </c>
       <c r="C16" s="7">
         <f>Nutrients!P17</f>
-        <v>33.6223</v>
+        <v>33.6266</v>
       </c>
       <c r="D16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E16" s="3">
         <f>IF(C16/F16&lt;0.02,0,ROUND(C16/10,0)*10)</f>
@@ -5835,7 +5847,7 @@
         <f t="shared" si="0"/>
         <v>0.02</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="10">
         <f t="shared" si="1"/>
         <v>0.026</v>
       </c>
@@ -5849,10 +5861,10 @@
       </c>
       <c r="C17" s="7">
         <f>Nutrients!Q17</f>
-        <v>1.0298</v>
+        <v>1.0302</v>
       </c>
       <c r="D17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E17" s="3">
         <f>IF(C17/F17&lt;0.02,0,ROUND(C17,1))</f>
@@ -5866,7 +5878,7 @@
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="10">
         <f t="shared" si="1"/>
         <v>0.057</v>
       </c>
@@ -5880,10 +5892,10 @@
       </c>
       <c r="C18" s="7">
         <f>Nutrients!R17</f>
-        <v>130.4153</v>
+        <v>130.3811</v>
       </c>
       <c r="D18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E18" s="3">
         <f>IF(C18/F18&lt;0.02,0,ROUND(C18/10,0)*10)</f>
@@ -5897,14 +5909,14 @@
         <f t="shared" si="0"/>
         <v>0.03</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="10">
         <f t="shared" si="1"/>
         <v>0.028</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -5927,7 +5939,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -5944,10 +5956,10 @@
         <v>95</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -6076,7 +6088,7 @@
         <v>roasted almond butter</v>
       </c>
       <c r="F9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -6100,7 +6112,7 @@
         <v>sliced almonds</v>
       </c>
       <c r="F10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -6176,7 +6188,7 @@
       </c>
       <c r="C14" s="9">
         <f>Formula!C15</f>
-        <v>0.72</v>
+        <v>0.81</v>
       </c>
       <c r="D14" t="str">
         <f>IF(Formula!F15="","",Formula!F15)</f>
@@ -6208,12 +6220,12 @@
         <v>soy lecithin</v>
       </c>
       <c r="F15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B17" t="str">
         <f>UPPER(LEFT(E4&amp;", "&amp;E5&amp;", "&amp;E6&amp;", "&amp;E7&amp;", "&amp;E8&amp;", "&amp;E9&amp;", "&amp;E10&amp;", "&amp;E11&amp;", "&amp;E12&amp;", "&amp;E13&amp;", "&amp;E14&amp;", "&amp;E15,1))&amp;MID(E4&amp;", "&amp;E5&amp;", "&amp;E6&amp;", "&amp;E7&amp;", "&amp;E8&amp;", "&amp;E9&amp;", "&amp;E10&amp;", "&amp;E11&amp;", "&amp;E12&amp;", "&amp;E13&amp;", "&amp;E14&amp;", "&amp;E15,2,900)&amp;"."</f>
@@ -6222,7 +6234,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B18" t="str">
         <f>"Contains: "&amp;IF(COUNTIF(F4:F15,"almonds")&gt;0,"almonds","")&amp;IF(COUNTIF(F4:F15,"soy")&gt;0,", soy","")&amp;"."</f>
@@ -6231,7 +6243,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19">
         <f>COUNTA(B4:B15)</f>
@@ -6240,7 +6252,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -6264,53 +6276,53 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C4" s="12">
+        <v>215</v>
+      </c>
+      <c r="C4" s="11">
         <f>Parameters!$B$11*100</f>
         <v>10</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <f>ROUND(Nutrients!K18/Parameters!B22*100,1)</f>
         <v>8.9</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <f>ROUND(Nutrients!K17/Parameters!B22*100,1)</f>
         <v>9.3</v>
       </c>
@@ -6319,42 +6331,42 @@
         <v>Not supported</v>
       </c>
       <c r="G4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B5" t="s">
-        <v>217</v>
-      </c>
-      <c r="C5" s="12">
+        <v>218</v>
+      </c>
+      <c r="C5" s="11">
         <f>Parameters!$B$13</f>
         <v>140</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <f>ROUND(Nutrients!I18,1)</f>
-        <v>123</v>
-      </c>
-      <c r="E5" s="12">
+        <v>135.9</v>
+      </c>
+      <c r="E5" s="11">
         <f>ROUND(Nutrients!I17,1)</f>
-        <v>129.1</v>
+        <v>142.7</v>
       </c>
       <c r="F5" t="str">
         <f>IF(AND(D5&lt;=C5,E5&lt;=C5),"Supported","Not supported")</f>
-        <v>Supported</v>
+        <v>Not supported</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C6" s="8">
         <f>Parameters!$B$14</f>
@@ -6370,34 +6382,34 @@
         <v>Supported</v>
       </c>
       <c r="G6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F7" t="str">
         <f>IF(COUNTIF(Formula!B4:B16,"*artificial*")=0,"Supported","Not supported")</f>
         <v>Supported</v>
       </c>
       <c r="G7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B8" t="s">
-        <v>225</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13">
+        <v>227</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12">
         <f>Rounding!E13</f>
         <v>8</v>
       </c>
@@ -6406,15 +6418,15 @@
         <v>Not supported</v>
       </c>
       <c r="G8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -6427,16 +6439,16 @@
         <v>Supported</v>
       </c>
       <c r="G9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B11">
         <f>COUNTIF(F4:F9,"Supported")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -6445,12 +6457,12 @@
       </c>
       <c r="B12">
         <f>COUNTIF(F4:F9,"Not supported")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/submissions/08-nutrition-panel-granola/solution/oat_cherry_bar_label_review.xlsx
+++ b/submissions/08-nutrition-panel-granola/solution/oat_cherry_bar_label_review.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AE37E7-603D-694E-951D-6728693D360A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E15DF1B-C041-6E45-B6C9-C3046C14AEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="243">
   <si>
     <t>Nutrition Facts, Oat and Cherry Bar, formula OCB-26-03, as the wrapper will print</t>
   </si>
@@ -405,6 +405,9 @@
     <t>Vanilla extract</t>
   </si>
   <si>
+    <t>vanilla bean extractives in water and alcohol, sugar, natural flavor</t>
+  </si>
+  <si>
     <t>RM-5031</t>
   </si>
   <si>
@@ -429,7 +432,7 @@
     <t>Grams per serving are batch kilograms over the finished batch weight times the serving weight, per SOP 1.1 and 1.3; the water leaves in the bake, so the sum of the grams exceeds the serving weight by the water and volatiles lost.</t>
   </si>
   <si>
-    <t>DECLARED_NAME is the common name on the formula in lower case under SOP 4.1; SUB_INGREDIENTS are typed from specification S-1187 revision 7 for the crisp rice and specification S-3301 revision 5 for the cherries, in the order each lists them.</t>
+    <t>DECLARED_NAME is the common name on the formula in lower case under SOP 4.1; SUB_INGREDIENTS are typed from specification S-1187 revision 7 for the crisp rice, S-3301 revision 5 for the cherries and S-5020 revision 2 for the vanilla extract, in the order each lists them.</t>
   </si>
   <si>
     <t>Supplier nutrient specifications from ingredient_nutrient_specs.csv and the specifications in force, and the same values normalised to 100 g per SOP 1.2</t>
@@ -534,7 +537,7 @@
     <t>Supplier spec S-1042 rev 4</t>
   </si>
   <si>
-    <t>Supplier spec S-2210 rev 2</t>
+    <t>Supplier spec S-2210 rev 3</t>
   </si>
   <si>
     <t>Supplier spec S-1187 rev 7</t>
@@ -558,7 +561,7 @@
     <t>Supplier spec S-4102 rev 3</t>
   </si>
   <si>
-    <t>Supplier spec S-5020 rev 1</t>
+    <t>Supplier spec S-5020 rev 2</t>
   </si>
   <si>
     <t>Supplier spec S-5031 rev 2</t>
@@ -573,7 +576,7 @@
     <t>BASIS_G is the weight each specification states its values on. The nutrient sheet marks the crisp rice and the almond butter as stated per serving; specification S-1187 is stated per 30 g serving and specification S-3120 per 32 g serving, and both are converted to 100 g in the right-hand block before use.</t>
   </si>
   <si>
-    <t>The cherries row carries specification S-3301 revision 5, the specification in force, in place of the revision 4 row on the nutrient sheet, which states total sugars at 58.0 g and no added sugars figure.</t>
+    <t>The cherries, brown rice syrup and vanilla extract rows carry their specifications in force (S-3301 revision 5, S-2210 revision 3 and S-5020 revision 2) in place of the nutrient sheet rows at revisions 4, 2 and 1, which state total sugars at 58.0 g with no added sugars figure, sodium at 43 mg, and no added sugar.</t>
   </si>
   <si>
     <t>Nutrient contribution of each ingredient to one serving, grams in the serving times the per-100 g specification over 100</t>
@@ -651,7 +654,7 @@
     <t>Ingredients declared</t>
   </si>
   <si>
-    <t>Water is left off under SOP 4.1 because it is removed in the bake. The almonds are named as the specific tree nut under 4.2, and the soy lecithin carries the soy declaration. The barley malt extract in the crisp rice is a gluten source and not a major food allergen, and specification S-1187 states that none is present in the product, so the Contains statement stays at almonds and soy. Specification S-3120 states the almond butter as dry roasted almonds alone, so it prints as a single ingredient.</t>
+    <t>Water is left off under SOP 4.1 because it is removed in the bake. The almonds are named as the specific tree nut under 4.2, and the soy lecithin carries the soy declaration. The barley malt extract in the crisp rice is a gluten source and not a major food allergen, and specification S-1187 states that none is present in the product, so the Contains statement stays at almonds and soy. Specification S-3120 states the almond butter as dry roasted almonds alone, so it prints as a single ingredient. Specification S-5020 revision 2 lists three sub-ingredients for the vanilla extract, so it prints as a compound ingredient despite the brief's line on compound items.</t>
   </si>
   <si>
     <t>Each claim in the product brief tested under SOP QA-14 section 5 on the unrounded amount per reference amount and per serving</t>
@@ -687,7 +690,7 @@
     <t>Fiber as percent of the 28 g daily value, both bases at or above the threshold</t>
   </si>
   <si>
-    <t>SOP 5.1; the panel declares 3 g at 11% because the declared value rounds up from 2.613 g, but the claim is tested on the unrounded amount</t>
+    <t>SOP 5.1; the panel declares 3 g at 11% because the declared value rounds up from 2.815 g, but the claim is tested on the unrounded amount on both bases</t>
   </si>
   <si>
     <t>Low sodium</t>
@@ -696,7 +699,7 @@
     <t>Sodium in mg, both bases at or below the ceiling</t>
   </si>
   <si>
-    <t>SOP 5.1 and 5.2; the bar clears the ceiling per reference amount and exceeds it per serving, and both must pass</t>
+    <t>SOP 5.1 and 5.2; specification S-2210 revision 3 at 2 mg of sodium per 100 g governs the syrup, and on the nutrient sheet row the serving would exceed the ceiling</t>
   </si>
   <si>
     <t>Made with whole grain oats</t>
@@ -705,7 +708,7 @@
     <t>Grams of whole grain rolled oats per serving at or above the floor</t>
   </si>
   <si>
-    <t>SOP 5.3, a company statement and not a federal nutrient content claim</t>
+    <t>SOP 5.3, a company statement; the oats are carried into the finished weight, where 42 g of formula would carry 13.86 g</t>
   </si>
   <si>
     <t>No artificial flavors</t>
@@ -714,7 +717,7 @@
     <t>No artificial flavor in the formula</t>
   </si>
   <si>
-    <t>Formula OCB-26-03 carries vanilla extract only, a natural extract under specification S-5020</t>
+    <t>Formula OCB-26-03 carries vanilla extract and barley malt extract as its only flavorings; specification S-5020 states natural vanillin and a natural flavor with no artificial flavor</t>
   </si>
   <si>
     <t>No added sugar</t>
@@ -723,7 +726,7 @@
     <t>No sugar, syrup, honey or other sugar-bearing ingredient added</t>
   </si>
   <si>
-    <t>SOP 5.2; brown rice syrup, honey, sugar-infused cherries and the sugar in the crisp rice are added, and the panel declares the added sugars shown</t>
+    <t>SOP 5.2; brown rice syrup, honey, sugar-infused cherries, the sweetened vanilla extract and the sugar in the crisp rice are added, and the panel declares the added sugars shown</t>
   </si>
   <si>
     <t>Real fruit</t>
@@ -747,22 +750,22 @@
     <t>Priya, this is the label review for the Oat and Cherry Bar, formula OCB-26-03. The panel on the first tab is what prints, and every declared value on it reads from the Rounding tab, which reads from the Nutrients tab, which reads from the Formula and Specs tabs; nothing on the panel is typed in. The serving is one bar at the 42 gram target net weight under SOP QA-14 section 1.3, not the 42.1 gram pilot average, and one bar is one serving because 42 grams sits between 67 and 200 percent of the 40 gram reference amount.</t>
   </si>
   <si>
-    <t>Two things in the inputs change the numbers beyond the cherries below, and they are worth knowing before legal asks. The nutrient sheet marks the crisp rice and the almond butter as stated per serving and gives no serving weight. Specification S-1187 states the crisp rice per 30 g serving, and specification S-3120 states the almond butter per 32 g serving. The Specs tab converts both to 100 g before use; taken as per 100 g they would understate the sodium from the crisp rice and the fat from the almond butter by more than two thirds. The pilot batch lost 12.72 kg in the bake, so every nutrient is carried into a finished batch weight of 107.28 kg at a yield of 0.8940. A bar at 42 grams carries the nutrients of 46.98 grams of formula.</t>
-  </si>
-  <si>
-    <t>The cherries drive the added sugars line, and the nutrient sheet is out of date on them. Its cherries row is still specification S-3301 revision 4, with total sugars at 58.0 g per 100 g and no added sugars figure. Revision 5 is the specification in force for every lot we hold, so the panel uses it under section 1.2. Revision 5 puts 30.0 g of the 60.0 g of sugars per 100 g as added, the sucrose taken up in the infusion. With the brown rice syrup and honey the bar carries 7.851 g of added sugars unrounded, declared as 8 g at 16 percent of the daily value, against 9.497 g of total sugars declared as 9 g. Taken from the nutrient sheet row, the added sugars line would print 7 g. The percent daily values are computed from the declared, rounded amount under section 3.1, which is why the added sugars line shows 16 percent and not 15.7.</t>
-  </si>
-  <si>
-    <t>The ingredient statement lists twelve ingredients in descending order of formula weight with water left off under section 4.1, each under its common name on the formula, and it reads: Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract, ground cinnamon, sea salt, soy lecithin. The two compound ingredients carry the sub-ingredients their specifications list, S-1187 revision 7 for the crisp rice and S-3301 revision 5 for the cherries. The Contains statement reads Contains almonds and soy; the barley malt extract in the crisp rice is a gluten source and not a major food allergen, and S-1187 states that none is present in the product.</t>
-  </si>
-  <si>
-    <t>On the claims. Good source of fiber is not supported. The panel declares 3 g of fiber at 11 percent of the daily value, because the declared value rounds up from 2.613 g, but section 5.1 tests the claim on the unrounded amount per reference amount and per serving. The bar carries 2.489 g per 40 g reference amount, which is 8.9 percent of the daily value, and 9.3 percent per 42 gram serving. Both fall short of 10 percent, so the claim cannot go on the wrapper as the formula stands. Low sodium is not supported either. The bar carries 135.9 mg per 40 g reference amount, which clears the 140 mg ceiling. It carries 142.7 mg per 42 gram serving, which does not, and section 5.1 requires both bases to pass. The panel prints 140 mg because section 2.4 rounds to the nearest 10 above 140, so the wrapper would show the ceiling figure beside a claim the bar does not meet.</t>
-  </si>
-  <si>
-    <t>Made with whole grain oats is supported as a company statement under section 5.3: the bar carries 15.50 g of whole grain rolled oats per serving against the 8 gram floor. No artificial flavors is supported; the only flavorings in the formula are the vanilla extract, which specification S-5020 states as a natural extract, and the barley malt extract inside the crisp rice, which S-1187 states is its only flavoring. Real fruit is supported on the dried tart cherries, 3.76 g per bar. No added sugar is not supported and cannot be: the formula adds brown rice syrup, honey, sugar-infused cherries and a crisp rice that carries sugar of its own, and the panel declares 8 g of added sugars, so section 5.2 rules the flag out however it is worded.</t>
-  </si>
-  <si>
-    <t>Things for you to decide or take to a supplier before the copy locks. First, the fiber claim comes off the front panel unless product development reopens the frozen formula; the nearest lift is the oats, and that is a formula change, not a wording change. Second, the no added sugar flag comes off; the sales lead should hear the 8 g figure rather than a softer claim. Third, the low sodium flag comes off as the formula stands. Cutting the sea salt from 0.81 kg to 0.79 kg per batch would bring the serving to 139.7 mg, and that is also a formula change. Fourth, purchasing should reissue the nutrient sheet with the cherries at revision 5 and with the serving weights beside the two per serving rows. Fifth, the Contains statement rests on the formula and the three specifications, and wheat, barley and peanuts do not belong in it. S-1187 says the crisp rice packing line also runs a wheat flake cereal, and S-3120 says the almond butter line runs peanut butter on alternate weeks. QA should decide whether a shared-line advisory prints under the Contains statement before the wrapper goes. The workbook cites every specification revision it used on the Specs tab.</t>
+    <t>Two things in the inputs change the numbers beyond the specification revisions below, and they are worth knowing before legal asks. The nutrient sheet marks the crisp rice and the almond butter as stated per serving and gives no serving weight. Specification S-1187 states the crisp rice per 30 g serving, and specification S-3120 states the almond butter per 32 g serving. The Specs tab converts both to 100 g before use; taken as per 100 g they would understate the sodium from the crisp rice and the fat from the almond butter by more than two thirds. The pilot batch lost 12.72 kg in the bake, so every nutrient is carried into a finished batch weight of 107.28 kg at a yield of 0.8940. A bar at 42 grams carries the nutrients of 46.98 grams of formula, and the whole grain statement turns on that: the bar carries 15.50 g of whole grain rolled oats against the 15 gram floor in section 5.3, where 42 grams of formula would carry only 13.86 g.</t>
+  </si>
+  <si>
+    <t>The nutrient sheet is out of date against three specifications in force, and section 1.2 says the specification in force governs. Its cherries row is still S-3301 revision 4, with total sugars at 58.0 g per 100 g and no added sugars figure; revision 5 puts 30.0 g of the 60.0 g of sugars per 100 g as added, the sucrose taken up in the infusion. Its brown rice syrup row is still S-2210 revision 2 at 43 mg of sodium per 100 g, and revision 3 states 2 mg after the plant move. Its vanilla extract row is still S-5020 revision 1 with no added sugar, and revision 2 states 12.7 g of added sugar per 100 g. With the syrup, the honey, the cherries and the vanilla the bar carries 7.929 g of added sugars unrounded, declared as 8 g at 16 percent of the daily value, against 9.497 g of total sugars declared as 9 g. Taken from the nutrient sheet rows, the added sugars line would print 7 g, and the sodium per serving would exceed 140 mg. The percent daily values are computed from the declared, rounded amount under section 3.1, which is why the added sugars line shows 16 percent and not 15.9.</t>
+  </si>
+  <si>
+    <t>The ingredient statement lists twelve ingredients in descending order of formula weight with water left off under section 4.1, each under its common name on the formula, and it reads: Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract (vanilla bean extractives in water and alcohol, sugar, natural flavor), ground cinnamon, sea salt, soy lecithin. Three compound ingredients carry the sub-ingredients their specifications list, S-1187 revision 7 for the crisp rice, S-3301 revision 5 for the cherries and S-5020 revision 2 for the vanilla extract. Purchasing's line in the brief that the cherries and the crisp rice are the only compound items does not hold: S-5020 revision 2 describes a two-fold extract with sugar and a natural flavor, and it prints as a compound ingredient. The Contains statement reads Contains almonds and soy; the barley malt extract in the crisp rice is a gluten source and not a major food allergen, and S-1187 states that none is present in the product.</t>
+  </si>
+  <si>
+    <t>On the claims. Good source of fiber is not supported, and it is close. The panel declares 3 g of fiber at 11 percent of the daily value, because the declared value rounds up from 2.815 g, but section 5.1 tests the claim on the unrounded amount per reference amount and per serving. The bar carries 2.815 g per 42 gram serving, which is 10.1 percent of the daily value and clears. It carries 2.681 g per 40 g reference amount, which is 9.6 percent and does not, and section 5.1 requires both bases. Low sodium is supported at 133.3 mg per reference amount and 139.9 mg per serving against the 140 mg ceiling. It holds only because the syrup is read at revision 3; on the nutrient sheet's 43 mg the serving would exceed the ceiling.</t>
+  </si>
+  <si>
+    <t>Made with whole grain oats is supported as a company statement under section 5.3: the bar carries 15.50 g of whole grain rolled oats per serving against the 15 gram floor, and the statement holds only with the yield applied. No artificial flavors is supported; the flavorings in the formula are the vanilla extract, which specification S-5020 states carries natural vanillin and a natural flavor only, and the barley malt extract inside the crisp rice. Real fruit is supported on the dried tart cherries, 3.76 g per bar. No added sugar is not supported and cannot be: the formula adds brown rice syrup, honey, sugar-infused cherries, a sweetened vanilla extract and a crisp rice that carries sugar of its own, and the panel declares 8 g of added sugars, so section 5.2 rules the flag out however it is worded. Calcium prints as 0 mg at 0 percent: the bar carries 25.707 mg, which is 1.98 percent of the daily value, and section 2.6 makes the 2 percent test on the unrounded amount before rounding; rounded first it would print 30 mg at 2 percent.</t>
+  </si>
+  <si>
+    <t>Things for you to decide or take to a supplier before the copy locks. First, the fiber claim comes off the front panel unless product development reopens the frozen formula; it clears per serving and misses per reference amount by 0.12 g, so a small lift in the oats would carry it. Second, the no added sugar flag comes off; the sales lead should hear the 8 g figure rather than a softer claim. Third, the crisp rice on hand: purchasing's receiving log puts 1,800 kg of the launch inventory in lots packed in September 2025, which carry the revision 6 declaration of rice, sugar, salt and malt flavor, while the wrapper prints the revision 7 sub-ingredients that govern the pilot and the later lots. Those lots either go to another product or the wrapper waits for them to be used up, and that is your call with purchasing. Fourth, purchasing should reissue the nutrient sheet with the cherries, the syrup and the vanilla at their revisions in force and with the serving weights beside the two per serving rows, and correct the brief's line on compound items. Fifth, the Contains statement rests on the formula and the specifications, and wheat, barley and peanuts do not belong in it. S-1187 says the crisp rice packing line also runs a wheat flake cereal, and S-3120 says the almond butter line runs peanut butter on alternate weeks. QA should decide whether a shared-line advisory prints under the Contains statement before the wrapper goes. The workbook cites every specification revision it used on the Specs tab.</t>
   </si>
 </sst>
 </file>
@@ -1428,14 +1431,14 @@
       </c>
       <c r="B19" s="3">
         <f>Rounding!E16</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C19" t="s">
         <v>19</v>
       </c>
       <c r="D19" s="4">
         <f>Rounding!G16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E19" t="s">
         <v>13</v>
@@ -1485,7 +1488,7 @@
       </c>
       <c r="B22" t="str">
         <f>'Ingredient Statement'!B17</f>
-        <v>Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract, ground cinnamon, sea salt, soy lecithin.</v>
+        <v>Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract (vanilla bean extractives in water and alcohol, sugar, natural flavor), ground cinnamon, sea salt, soy lecithin.</v>
       </c>
       <c r="E22" t="s">
         <v>32</v>
@@ -1509,7 +1512,7 @@
       </c>
       <c r="B24">
         <f>Claims!B11</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" t="s">
         <v>35</v>
@@ -1521,7 +1524,7 @@
       </c>
       <c r="B25">
         <f>Claims!B12</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" t="s">
         <v>35</v>
@@ -1547,42 +1550,42 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -1737,7 +1740,7 @@
         <v>61</v>
       </c>
       <c r="B14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
         <v>62</v>
@@ -2389,6 +2392,9 @@
         <f>LOWER(B13)</f>
         <v>vanilla extract</v>
       </c>
+      <c r="F13" t="s">
+        <v>122</v>
+      </c>
       <c r="G13" s="7">
         <f>ROUND(C13/Parameters!$B$7*Parameters!$B$5,4)</f>
         <v>0.6107</v>
@@ -2404,10 +2410,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C14" s="9">
         <v>0.84</v>
@@ -2435,10 +2441,10 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C15" s="9">
         <v>0.81</v>
@@ -2466,10 +2472,10 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="9">
         <v>0.48</v>
@@ -2497,7 +2503,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="9">
         <f>ROUND(SUM(C4:C16),3)</f>
@@ -2514,12 +2520,12 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2542,7 +2548,7 @@
   <sheetData>
     <row r="1" spans="1:36" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.2">
@@ -2553,103 +2559,103 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>70</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AJ3" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
@@ -2684,7 +2690,7 @@
         <v>67.7</v>
       </c>
       <c r="K4">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -2699,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="Q4">
         <v>4.25</v>
@@ -2708,7 +2714,7 @@
         <v>362</v>
       </c>
       <c r="S4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="U4" t="str">
         <f t="shared" ref="U4:U16" si="0">A4</f>
@@ -2744,7 +2750,7 @@
       </c>
       <c r="AC4" s="7">
         <f t="shared" ref="AC4:AC16" si="8">ROUND(K4/$C4*100,4)</f>
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="AD4" s="7">
         <f t="shared" ref="AD4:AD16" si="9">ROUND(L4/$C4*100,4)</f>
@@ -2764,7 +2770,7 @@
       </c>
       <c r="AH4" s="7">
         <f t="shared" ref="AH4:AH16" si="13">ROUND(P4/$C4*100,4)</f>
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AI4" s="7">
         <f t="shared" ref="AI4:AI16" si="14">ROUND(Q4/$C4*100,4)</f>
@@ -2801,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>78</v>
@@ -2831,7 +2837,7 @@
         <v>62</v>
       </c>
       <c r="S5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="0"/>
@@ -2859,7 +2865,7 @@
       </c>
       <c r="AA5" s="7">
         <f t="shared" si="6"/>
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="AB5" s="7">
         <f t="shared" si="7"/>
@@ -2954,7 +2960,7 @@
         <v>28</v>
       </c>
       <c r="S6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
@@ -3077,7 +3083,7 @@
         <v>52</v>
       </c>
       <c r="S7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="0"/>
@@ -3200,7 +3206,7 @@
         <v>380</v>
       </c>
       <c r="S8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U8" t="str">
         <f t="shared" si="0"/>
@@ -3314,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="Q9">
         <v>1.12</v>
@@ -3323,7 +3329,7 @@
         <v>239</v>
       </c>
       <c r="S9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="0"/>
@@ -3379,7 +3385,7 @@
       </c>
       <c r="AH9" s="7">
         <f t="shared" si="13"/>
-        <v>346.875</v>
+        <v>203.125</v>
       </c>
       <c r="AI9" s="7">
         <f t="shared" si="14"/>
@@ -3437,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="Q10">
         <v>3.71</v>
@@ -3446,7 +3452,7 @@
         <v>733</v>
       </c>
       <c r="S10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="U10" t="str">
         <f t="shared" si="0"/>
@@ -3502,7 +3508,7 @@
       </c>
       <c r="AH10" s="7">
         <f t="shared" si="13"/>
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="AI10" s="7">
         <f t="shared" si="14"/>
@@ -3569,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="U11" t="str">
         <f t="shared" si="0"/>
@@ -3692,7 +3698,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="U12" t="str">
         <f t="shared" si="0"/>
@@ -3797,7 +3803,7 @@
         <v>12.7</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="N13">
         <v>0.1</v>
@@ -3815,7 +3821,7 @@
         <v>148</v>
       </c>
       <c r="S13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="U13" t="str">
         <f t="shared" si="0"/>
@@ -3859,7 +3865,7 @@
       </c>
       <c r="AE13" s="7">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="AF13" s="7">
         <f t="shared" si="11"/>
@@ -3884,10 +3890,10 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -3938,7 +3944,7 @@
         <v>431</v>
       </c>
       <c r="S14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U14" t="str">
         <f t="shared" si="0"/>
@@ -4007,10 +4013,10 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -4061,7 +4067,7 @@
         <v>8</v>
       </c>
       <c r="S15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="U15" t="str">
         <f t="shared" si="0"/>
@@ -4130,10 +4136,10 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -4184,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="U16" t="str">
         <f t="shared" si="0"/>
@@ -4253,12 +4259,12 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4279,7 +4285,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -4293,49 +4299,49 @@
         <v>96</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
@@ -4381,7 +4387,7 @@
       </c>
       <c r="K4" s="7">
         <f>ROUND($C4/100*Specs!AC4,4)</f>
-        <v>1.5658</v>
+        <v>1.7674</v>
       </c>
       <c r="L4" s="7">
         <f>ROUND($C4/100*Specs!AD4,4)</f>
@@ -4401,7 +4407,7 @@
       </c>
       <c r="P4" s="7">
         <f>ROUND($C4/100*Specs!AH4,4)</f>
-        <v>8.0618</v>
+        <v>6.9765</v>
       </c>
       <c r="Q4" s="7">
         <f>ROUND($C4/100*Specs!AI4,4)</f>
@@ -4447,7 +4453,7 @@
       </c>
       <c r="I5" s="7">
         <f>ROUND($C5/100*Specs!AA5,4)</f>
-        <v>2.9292</v>
+        <v>0.1362</v>
       </c>
       <c r="J5" s="7">
         <f>ROUND($C5/100*Specs!AB5,4)</f>
@@ -4771,7 +4777,7 @@
       </c>
       <c r="P9" s="7">
         <f>ROUND($C9/100*Specs!AH9,4)</f>
-        <v>11.4073</v>
+        <v>6.68</v>
       </c>
       <c r="Q9" s="7">
         <f>ROUND($C9/100*Specs!AI9,4)</f>
@@ -4845,7 +4851,7 @@
       </c>
       <c r="P10" s="7">
         <f>ROUND($C10/100*Specs!AH10,4)</f>
-        <v>8.2145</v>
+        <v>6.1074</v>
       </c>
       <c r="Q10" s="7">
         <f>ROUND($C10/100*Specs!AI10,4)</f>
@@ -5055,7 +5061,7 @@
       </c>
       <c r="M13" s="7">
         <f>ROUND($C13/100*Specs!AE13,4)</f>
-        <v>0</v>
+        <v>0.0776</v>
       </c>
       <c r="N13" s="7">
         <f>ROUND($C13/100*Specs!AF13,4)</f>
@@ -5302,7 +5308,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C17" s="7">
         <f>ROUND(SUM(C4:C16),4)</f>
@@ -5330,7 +5336,7 @@
       </c>
       <c r="I17" s="7">
         <f t="shared" si="0"/>
-        <v>142.7292</v>
+        <v>139.9362</v>
       </c>
       <c r="J17" s="7">
         <f t="shared" si="0"/>
@@ -5338,7 +5344,7 @@
       </c>
       <c r="K17" s="7">
         <f t="shared" si="0"/>
-        <v>2.6133</v>
+        <v>2.8149</v>
       </c>
       <c r="L17" s="7">
         <f t="shared" si="0"/>
@@ -5346,7 +5352,7 @@
       </c>
       <c r="M17" s="7">
         <f t="shared" si="0"/>
-        <v>7.8514</v>
+        <v>7.929</v>
       </c>
       <c r="N17" s="7">
         <f t="shared" si="0"/>
@@ -5358,7 +5364,7 @@
       </c>
       <c r="P17" s="7">
         <f t="shared" si="0"/>
-        <v>33.6266</v>
+        <v>25.7069</v>
       </c>
       <c r="Q17" s="7">
         <f t="shared" si="0"/>
@@ -5371,7 +5377,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D18" s="7">
         <f>ROUND(D17*Parameters!$B$4/Parameters!$B$5,4)</f>
@@ -5395,7 +5401,7 @@
       </c>
       <c r="I18" s="7">
         <f>ROUND(I17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>135.9326</v>
+        <v>133.2726</v>
       </c>
       <c r="J18" s="7">
         <f>ROUND(J17*Parameters!$B$4/Parameters!$B$5,4)</f>
@@ -5403,7 +5409,7 @@
       </c>
       <c r="K18" s="7">
         <f>ROUND(K17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>2.4889</v>
+        <v>2.6809</v>
       </c>
       <c r="L18" s="7">
         <f>ROUND(L17*Parameters!$B$4/Parameters!$B$5,4)</f>
@@ -5411,7 +5417,7 @@
       </c>
       <c r="M18" s="7">
         <f>ROUND(M17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>7.4775</v>
+        <v>7.5514</v>
       </c>
       <c r="N18" s="7">
         <f>ROUND(N17*Parameters!$B$4/Parameters!$B$5,4)</f>
@@ -5423,7 +5429,7 @@
       </c>
       <c r="P18" s="7">
         <f>ROUND(P17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>32.0253</v>
+        <v>24.4828</v>
       </c>
       <c r="Q18" s="7">
         <f>ROUND(Q17*Parameters!$B$4/Parameters!$B$5,4)</f>
@@ -5436,7 +5442,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -5459,7 +5465,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -5470,10 +5476,10 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>3</v>
@@ -5485,7 +5491,7 @@
         <v>5</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -5497,7 +5503,7 @@
         <v>183.6219</v>
       </c>
       <c r="D4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E4" s="3">
         <f>IF(C4&lt;5,0,IF(C4&lt;=50,ROUND(C4/5,0)*5,ROUND(C4/10,0)*10))</f>
@@ -5516,7 +5522,7 @@
         <v>6.7655</v>
       </c>
       <c r="D5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E5" s="3">
         <f>IF(C5&lt;0.5,0,IF(C5&lt;5,ROUND(C5/0.5,0)*0.5,ROUND(C5,0)))</f>
@@ -5547,7 +5553,7 @@
         <v>0.6485</v>
       </c>
       <c r="D6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E6" s="3">
         <f>IF(C6&lt;0.5,0,IF(C6&lt;5,ROUND(C6/0.5,0)*0.5,ROUND(C6,0)))</f>
@@ -5578,7 +5584,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E7" s="3">
         <f>IF(C7&lt;0.5,0,IF(C7&lt;5,ROUND(C7/0.5,0)*0.5,ROUND(C7,0)))</f>
@@ -5597,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E8" s="3">
         <f>IF(C8&lt;2,0,IF(C8&lt;=5,"less than 5",ROUND(C8/5,0)*5))</f>
@@ -5625,10 +5631,10 @@
       </c>
       <c r="C9" s="7">
         <f>Nutrients!I17</f>
-        <v>142.7292</v>
+        <v>139.9362</v>
       </c>
       <c r="D9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E9" s="3">
         <f>IF(C9&lt;5,0,IF(C9&lt;=140,ROUND(C9/5,0)*5,ROUND(C9/10,0)*10))</f>
@@ -5644,7 +5650,7 @@
       </c>
       <c r="H9" s="10">
         <f>ROUND(C9/F9,3)</f>
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -5659,7 +5665,7 @@
         <v>27.8126</v>
       </c>
       <c r="D10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E10" s="3">
         <f>IF(C10&lt;0.5,0,IF(C10&lt;1,"less than 1",ROUND(C10,0)))</f>
@@ -5687,10 +5693,10 @@
       </c>
       <c r="C11" s="7">
         <f>Nutrients!K17</f>
-        <v>2.6133</v>
+        <v>2.8149</v>
       </c>
       <c r="D11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E11" s="3">
         <f>IF(C11&lt;0.5,0,IF(C11&lt;1,"less than 1",ROUND(C11,0)))</f>
@@ -5706,7 +5712,7 @@
       </c>
       <c r="H11" s="10">
         <f>ROUND(C11/F11,3)</f>
-        <v>0.093</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -5721,7 +5727,7 @@
         <v>9.497</v>
       </c>
       <c r="D12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E12" s="3">
         <f>IF(C12&lt;0.5,0,IF(C12&lt;1,"less than 1",ROUND(C12,0)))</f>
@@ -5737,10 +5743,10 @@
       </c>
       <c r="C13" s="7">
         <f>Nutrients!M17</f>
-        <v>7.8514</v>
+        <v>7.929</v>
       </c>
       <c r="D13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E13" s="3">
         <f>IF(C13&lt;0.5,0,IF(C13&lt;1,"less than 1",ROUND(C13,0)))</f>
@@ -5756,7 +5762,7 @@
       </c>
       <c r="H13" s="10">
         <f t="shared" ref="H13:H18" si="1">ROUND(C13/F13,3)</f>
-        <v>0.157</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -5771,7 +5777,7 @@
         <v>3.8276</v>
       </c>
       <c r="D14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E14" s="3">
         <f>IF(C14&lt;0.5,0,IF(C14&lt;1,"less than 1",ROUND(C14,0)))</f>
@@ -5802,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E15" s="3">
         <f>IF(C15/F15&lt;0.02,0,ROUND(C15,1))</f>
@@ -5830,14 +5836,14 @@
       </c>
       <c r="C16" s="7">
         <f>Nutrients!P17</f>
-        <v>33.6266</v>
+        <v>25.7069</v>
       </c>
       <c r="D16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E16" s="3">
         <f>IF(C16/F16&lt;0.02,0,ROUND(C16/10,0)*10)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <f>Parameters!B26</f>
@@ -5845,11 +5851,11 @@
       </c>
       <c r="G16" s="4">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H16" s="10">
         <f t="shared" si="1"/>
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -5864,7 +5870,7 @@
         <v>1.0302</v>
       </c>
       <c r="D17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E17" s="3">
         <f>IF(C17/F17&lt;0.02,0,ROUND(C17,1))</f>
@@ -5895,7 +5901,7 @@
         <v>130.3811</v>
       </c>
       <c r="D18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E18" s="3">
         <f>IF(C18/F18&lt;0.02,0,ROUND(C18/10,0)*10)</f>
@@ -5916,7 +5922,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -5939,7 +5945,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -5956,10 +5962,10 @@
         <v>95</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -6088,7 +6094,7 @@
         <v>roasted almond butter</v>
       </c>
       <c r="F9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -6112,7 +6118,7 @@
         <v>sliced almonds</v>
       </c>
       <c r="F10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -6150,11 +6156,11 @@
       </c>
       <c r="D12" t="str">
         <f>IF(Formula!F13="","",Formula!F13)</f>
-        <v/>
+        <v>vanilla bean extractives in water and alcohol, sugar, natural flavor</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
-        <v>vanilla extract</v>
+        <v>vanilla extract (vanilla bean extractives in water and alcohol, sugar, natural flavor)</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -6220,21 +6226,21 @@
         <v>soy lecithin</v>
       </c>
       <c r="F15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B17" t="str">
         <f>UPPER(LEFT(E4&amp;", "&amp;E5&amp;", "&amp;E6&amp;", "&amp;E7&amp;", "&amp;E8&amp;", "&amp;E9&amp;", "&amp;E10&amp;", "&amp;E11&amp;", "&amp;E12&amp;", "&amp;E13&amp;", "&amp;E14&amp;", "&amp;E15,1))&amp;MID(E4&amp;", "&amp;E5&amp;", "&amp;E6&amp;", "&amp;E7&amp;", "&amp;E8&amp;", "&amp;E9&amp;", "&amp;E10&amp;", "&amp;E11&amp;", "&amp;E12&amp;", "&amp;E13&amp;", "&amp;E14&amp;", "&amp;E15,2,900)&amp;"."</f>
-        <v>Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract, ground cinnamon, sea salt, soy lecithin.</v>
+        <v>Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract (vanilla bean extractives in water and alcohol, sugar, natural flavor), ground cinnamon, sea salt, soy lecithin.</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B18" t="str">
         <f>"Contains: "&amp;IF(COUNTIF(F4:F15,"almonds")&gt;0,"almonds","")&amp;IF(COUNTIF(F4:F15,"soy")&gt;0,", soy","")&amp;"."</f>
@@ -6243,7 +6249,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B19">
         <f>COUNTA(B4:B15)</f>
@@ -6252,7 +6258,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -6276,43 +6282,43 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C4" s="11">
         <f>Parameters!$B$11*100</f>
@@ -6320,26 +6326,26 @@
       </c>
       <c r="D4" s="11">
         <f>ROUND(Nutrients!K18/Parameters!B22*100,1)</f>
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="E4" s="11">
         <f>ROUND(Nutrients!K17/Parameters!B22*100,1)</f>
-        <v>9.3</v>
+        <v>10.1</v>
       </c>
       <c r="F4" t="str">
         <f>IF(AND(D4&gt;=C4,E4&gt;=C4),"Supported","Not supported")</f>
         <v>Not supported</v>
       </c>
       <c r="G4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C5" s="11">
         <f>Parameters!$B$13</f>
@@ -6347,30 +6353,30 @@
       </c>
       <c r="D5" s="11">
         <f>ROUND(Nutrients!I18,1)</f>
-        <v>135.9</v>
+        <v>133.3</v>
       </c>
       <c r="E5" s="11">
         <f>ROUND(Nutrients!I17,1)</f>
-        <v>142.7</v>
+        <v>139.9</v>
       </c>
       <c r="F5" t="str">
         <f>IF(AND(D5&lt;=C5,E5&lt;=C5),"Supported","Not supported")</f>
-        <v>Not supported</v>
+        <v>Supported</v>
       </c>
       <c r="G5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C6" s="8">
         <f>Parameters!$B$14</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8">
@@ -6382,30 +6388,30 @@
         <v>Supported</v>
       </c>
       <c r="G6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F7" t="str">
         <f>IF(COUNTIF(Formula!B4:B16,"*artificial*")=0,"Supported","Not supported")</f>
         <v>Supported</v>
       </c>
       <c r="G7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
@@ -6418,15 +6424,15 @@
         <v>Not supported</v>
       </c>
       <c r="G8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -6439,16 +6445,16 @@
         <v>Supported</v>
       </c>
       <c r="G9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B11">
         <f>COUNTIF(F4:F9,"Supported")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -6457,12 +6463,12 @@
       </c>
       <c r="B12">
         <f>COUNTIF(F4:F9,"Not supported")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/submissions/08-nutrition-panel-granola/solution/oat_cherry_bar_label_review.xlsx
+++ b/submissions/08-nutrition-panel-granola/solution/oat_cherry_bar_label_review.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E15DF1B-C041-6E45-B6C9-C3046C14AEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC37190-4944-3149-92E1-0B404B9D152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,8 @@
     <sheet name="Rounding" sheetId="7" r:id="rId7"/>
     <sheet name="Ingredient Statement" sheetId="8" r:id="rId8"/>
     <sheet name="Claims" sheetId="9" r:id="rId9"/>
-    <sheet name="Note to Priya" sheetId="10" r:id="rId10"/>
+    <sheet name="Inventory Check" sheetId="10" r:id="rId10"/>
+    <sheet name="Note to Priya" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="269">
   <si>
     <t>Nutrition Facts, Oat and Cherry Bar, formula OCB-26-03, as the wrapper will print</t>
   </si>
@@ -150,6 +151,18 @@
     <t>Claims not supported</t>
   </si>
   <si>
+    <t>Panel holds for all launch inventory</t>
+  </si>
+  <si>
+    <t>Inventory Check</t>
+  </si>
+  <si>
+    <t>Ingredient statement holds for all launch inventory</t>
+  </si>
+  <si>
+    <t>Low sodium flag holds for all launch inventory</t>
+  </si>
+  <si>
     <t>The footnote prints as the standard daily value statement; values read from the tab named beside each line, and the Rounding tab shows each unrounded figure beside its declared value.</t>
   </si>
   <si>
@@ -186,7 +199,7 @@
     <t>Finished batch weight, net of trim (kg)</t>
   </si>
   <si>
-    <t>Pilot batch record; SOP 1.1</t>
+    <t>Pilot batch record scale ticket less trim; SOP 1.1</t>
   </si>
   <si>
     <t>Yield, finished over input</t>
@@ -240,6 +253,12 @@
     <t>Daily value</t>
   </si>
   <si>
+    <t>Bars cut times the target weight (g), for reference</t>
+  </si>
+  <si>
+    <t>Not the yield basis; SOP 1.1 takes the scale ticket net of trim</t>
+  </si>
+  <si>
     <t>Pilot batch record, copied from formula_ocb_26_03.xlsx</t>
   </si>
   <si>
@@ -420,6 +439,9 @@
     <t>Sea salt</t>
   </si>
   <si>
+    <t>sea salt, calcium silicate</t>
+  </si>
+  <si>
     <t>RM-5055</t>
   </si>
   <si>
@@ -432,7 +454,7 @@
     <t>Grams per serving are batch kilograms over the finished batch weight times the serving weight, per SOP 1.1 and 1.3; the water leaves in the bake, so the sum of the grams exceeds the serving weight by the water and volatiles lost.</t>
   </si>
   <si>
-    <t>DECLARED_NAME is the common name on the formula in lower case under SOP 4.1; SUB_INGREDIENTS are typed from specification S-1187 revision 7 for the crisp rice, S-3301 revision 5 for the cherries and S-5020 revision 2 for the vanilla extract, in the order each lists them.</t>
+    <t>DECLARED_NAME is the common name on the formula in lower case under SOP 4.1; SUB_INGREDIENTS are typed from specification S-1187 revision 7 for the crisp rice, S-3301 revision 5 for the cherries, S-5020 revision 2 for the vanilla extract and S-5040 revision 1 for the sea salt, in the order each lists them.</t>
   </si>
   <si>
     <t>Supplier nutrient specifications from ingredient_nutrient_specs.csv and the specifications in force, and the same values normalised to 100 g per SOP 1.2</t>
@@ -654,7 +676,7 @@
     <t>Ingredients declared</t>
   </si>
   <si>
-    <t>Water is left off under SOP 4.1 because it is removed in the bake. The almonds are named as the specific tree nut under 4.2, and the soy lecithin carries the soy declaration. The barley malt extract in the crisp rice is a gluten source and not a major food allergen, and specification S-1187 states that none is present in the product, so the Contains statement stays at almonds and soy. Specification S-3120 states the almond butter as dry roasted almonds alone, so it prints as a single ingredient. Specification S-5020 revision 2 lists three sub-ingredients for the vanilla extract, so it prints as a compound ingredient despite the brief's line on compound items.</t>
+    <t>Water is left off under SOP 4.1 because it is removed in the bake. The almonds are named as the specific tree nut under 4.2, and the soy lecithin carries the soy declaration. The barley malt extract in the crisp rice is a gluten source and not a major food allergen, and specification S-1187 states that none is present in the product, so the Contains statement stays at almonds and soy. Specification S-3120 states the almond butter as dry roasted almonds alone, so it prints as a single ingredient. Specification S-5020 revision 2 lists three sub-ingredients for the vanilla extract, so it prints as a compound ingredient despite the brief's line on compound items. Specification S-5040 lists calcium silicate after the sea salt, so the salt prints as a compound ingredient as well.</t>
   </si>
   <si>
     <t>Each claim in the product brief tested under SOP QA-14 section 5 on the unrounded amount per reference amount and per serving</t>
@@ -699,7 +721,7 @@
     <t>Sodium in mg, both bases at or below the ceiling</t>
   </si>
   <si>
-    <t>SOP 5.1 and 5.2; specification S-2210 revision 3 at 2 mg of sodium per 100 g governs the syrup, and on the nutrient sheet row the serving would exceed the ceiling</t>
+    <t>SOP 5.1 and 5.2; specification S-2210 revision 3 at 2 mg of sodium per 100 g governs the syrup, and on the nutrient sheet row or on a bar-count yield the serving would exceed the ceiling</t>
   </si>
   <si>
     <t>Made with whole grain oats</t>
@@ -708,7 +730,7 @@
     <t>Grams of whole grain rolled oats per serving at or above the floor</t>
   </si>
   <si>
-    <t>SOP 5.3, a company statement; the oats are carried into the finished weight, where 42 g of formula would carry 13.86 g</t>
+    <t>SOP 5.3, a company statement; the oats alone are counted, and the brown rice syrup, made from whole grain brown rice per S-2210, is a derivative the rule excludes</t>
   </si>
   <si>
     <t>No artificial flavors</t>
@@ -744,28 +766,85 @@
     <t>Per reference amount is the 40 g reference amount customarily consumed; per serving is the 42 g bar. Section 5.1 requires both to pass.</t>
   </si>
   <si>
+    <t>Launch inventory check: whether the panel, the ingredient statement and the low sodium flag hold for every crisp rice lot on hand</t>
+  </si>
+  <si>
+    <t>Lot group</t>
+  </si>
+  <si>
+    <t>Pack dates</t>
+  </si>
+  <si>
+    <t>Quantity (kg)</t>
+  </si>
+  <si>
+    <t>S-1187 revision</t>
+  </si>
+  <si>
+    <t>Sodium per 30 g serving (mg)</t>
+  </si>
+  <si>
+    <t>Sub-ingredients declared</t>
+  </si>
+  <si>
+    <t>Pilot and later lots</t>
+  </si>
+  <si>
+    <t>November and December 2025</t>
+  </si>
+  <si>
+    <t>September 2025 lots</t>
+  </si>
+  <si>
+    <t>September 2025</t>
+  </si>
+  <si>
+    <t>rice, sugar, salt, malt flavor</t>
+  </si>
+  <si>
+    <t>Sources: the product brief's receiving log line, S-1187 revision 7 and its note on revision 6</t>
+  </si>
+  <si>
+    <t>Measure</t>
+  </si>
+  <si>
+    <t>Sodium per serving (mg)</t>
+  </si>
+  <si>
+    <t>Sodium declared (mg)</t>
+  </si>
+  <si>
+    <t>Low sodium, per serving against the ceiling</t>
+  </si>
+  <si>
+    <t>Crisp rice as it prints</t>
+  </si>
+  <si>
+    <t>Revision 7 governs the pilot and the lots packed after October 1, 2025. The September 2025 lots carry the revision 6 declaration and the revision 6 sodium stated in the S-1187 note on the superseded revision, and the sodium per serving on those lots replaces the crisp rice contribution alone, every other ingredient unchanged.</t>
+  </si>
+  <si>
     <t>Note to Priya Raman on the Oat and Cherry Bar label review</t>
   </si>
   <si>
-    <t>Priya, this is the label review for the Oat and Cherry Bar, formula OCB-26-03. The panel on the first tab is what prints, and every declared value on it reads from the Rounding tab, which reads from the Nutrients tab, which reads from the Formula and Specs tabs; nothing on the panel is typed in. The serving is one bar at the 42 gram target net weight under SOP QA-14 section 1.3, not the 42.1 gram pilot average, and one bar is one serving because 42 grams sits between 67 and 200 percent of the 40 gram reference amount.</t>
-  </si>
-  <si>
-    <t>Two things in the inputs change the numbers beyond the specification revisions below, and they are worth knowing before legal asks. The nutrient sheet marks the crisp rice and the almond butter as stated per serving and gives no serving weight. Specification S-1187 states the crisp rice per 30 g serving, and specification S-3120 states the almond butter per 32 g serving. The Specs tab converts both to 100 g before use; taken as per 100 g they would understate the sodium from the crisp rice and the fat from the almond butter by more than two thirds. The pilot batch lost 12.72 kg in the bake, so every nutrient is carried into a finished batch weight of 107.28 kg at a yield of 0.8940. A bar at 42 grams carries the nutrients of 46.98 grams of formula, and the whole grain statement turns on that: the bar carries 15.50 g of whole grain rolled oats against the 15 gram floor in section 5.3, where 42 grams of formula would carry only 13.86 g.</t>
-  </si>
-  <si>
-    <t>The nutrient sheet is out of date against three specifications in force, and section 1.2 says the specification in force governs. Its cherries row is still S-3301 revision 4, with total sugars at 58.0 g per 100 g and no added sugars figure; revision 5 puts 30.0 g of the 60.0 g of sugars per 100 g as added, the sucrose taken up in the infusion. Its brown rice syrup row is still S-2210 revision 2 at 43 mg of sodium per 100 g, and revision 3 states 2 mg after the plant move. Its vanilla extract row is still S-5020 revision 1 with no added sugar, and revision 2 states 12.7 g of added sugar per 100 g. With the syrup, the honey, the cherries and the vanilla the bar carries 7.929 g of added sugars unrounded, declared as 8 g at 16 percent of the daily value, against 9.497 g of total sugars declared as 9 g. Taken from the nutrient sheet rows, the added sugars line would print 7 g, and the sodium per serving would exceed 140 mg. The percent daily values are computed from the declared, rounded amount under section 3.1, which is why the added sugars line shows 16 percent and not 15.9.</t>
-  </si>
-  <si>
-    <t>The ingredient statement lists twelve ingredients in descending order of formula weight with water left off under section 4.1, each under its common name on the formula, and it reads: Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract (vanilla bean extractives in water and alcohol, sugar, natural flavor), ground cinnamon, sea salt, soy lecithin. Three compound ingredients carry the sub-ingredients their specifications list, S-1187 revision 7 for the crisp rice, S-3301 revision 5 for the cherries and S-5020 revision 2 for the vanilla extract. Purchasing's line in the brief that the cherries and the crisp rice are the only compound items does not hold: S-5020 revision 2 describes a two-fold extract with sugar and a natural flavor, and it prints as a compound ingredient. The Contains statement reads Contains almonds and soy; the barley malt extract in the crisp rice is a gluten source and not a major food allergen, and S-1187 states that none is present in the product.</t>
-  </si>
-  <si>
-    <t>On the claims. Good source of fiber is not supported, and it is close. The panel declares 3 g of fiber at 11 percent of the daily value, because the declared value rounds up from 2.815 g, but section 5.1 tests the claim on the unrounded amount per reference amount and per serving. The bar carries 2.815 g per 42 gram serving, which is 10.1 percent of the daily value and clears. It carries 2.681 g per 40 g reference amount, which is 9.6 percent and does not, and section 5.1 requires both bases. Low sodium is supported at 133.3 mg per reference amount and 139.9 mg per serving against the 140 mg ceiling. It holds only because the syrup is read at revision 3; on the nutrient sheet's 43 mg the serving would exceed the ceiling.</t>
-  </si>
-  <si>
-    <t>Made with whole grain oats is supported as a company statement under section 5.3: the bar carries 15.50 g of whole grain rolled oats per serving against the 15 gram floor, and the statement holds only with the yield applied. No artificial flavors is supported; the flavorings in the formula are the vanilla extract, which specification S-5020 states carries natural vanillin and a natural flavor only, and the barley malt extract inside the crisp rice. Real fruit is supported on the dried tart cherries, 3.76 g per bar. No added sugar is not supported and cannot be: the formula adds brown rice syrup, honey, sugar-infused cherries, a sweetened vanilla extract and a crisp rice that carries sugar of its own, and the panel declares 8 g of added sugars, so section 5.2 rules the flag out however it is worded. Calcium prints as 0 mg at 0 percent: the bar carries 25.707 mg, which is 1.98 percent of the daily value, and section 2.6 makes the 2 percent test on the unrounded amount before rounding; rounded first it would print 30 mg at 2 percent.</t>
-  </si>
-  <si>
-    <t>Things for you to decide or take to a supplier before the copy locks. First, the fiber claim comes off the front panel unless product development reopens the frozen formula; it clears per serving and misses per reference amount by 0.12 g, so a small lift in the oats would carry it. Second, the no added sugar flag comes off; the sales lead should hear the 8 g figure rather than a softer claim. Third, the crisp rice on hand: purchasing's receiving log puts 1,800 kg of the launch inventory in lots packed in September 2025, which carry the revision 6 declaration of rice, sugar, salt and malt flavor, while the wrapper prints the revision 7 sub-ingredients that govern the pilot and the later lots. Those lots either go to another product or the wrapper waits for them to be used up, and that is your call with purchasing. Fourth, purchasing should reissue the nutrient sheet with the cherries, the syrup and the vanilla at their revisions in force and with the serving weights beside the two per serving rows, and correct the brief's line on compound items. Fifth, the Contains statement rests on the formula and the specifications, and wheat, barley and peanuts do not belong in it. S-1187 says the crisp rice packing line also runs a wheat flake cereal, and S-3120 says the almond butter line runs peanut butter on alternate weeks. QA should decide whether a shared-line advisory prints under the Contains statement before the wrapper goes. The workbook cites every specification revision it used on the Specs tab.</t>
+    <t>Priya, this is the label review for the Oat and Cherry Bar, formula OCB-26-03. The panel on the first tab is what prints, and every declared value on it reads from the Rounding tab, which reads from the Nutrients tab, which reads from the Formula and Specs tabs; nothing on the panel is typed in. The serving is one bar at the 42 gram target net weight under SOP QA-14 section 1.3, not the 42.1 gram pilot average, and one bar is one serving because 42 grams sits between 67 and 200 percent of the 40 gram reference amount. The yield rests on the scale ticket net of trim, 107.28 kg, under section 1.1. The 2,520 bars cut times the target weight give 105,840 g, and that figure is not the yield basis; on it the sodium per serving would cross the ceiling.</t>
+  </si>
+  <si>
+    <t>Two things in the inputs change the numbers beyond the specification revisions below, and they are worth knowing before legal asks. The nutrient sheet marks the crisp rice and the almond butter as stated per serving and gives no serving weight. Specification S-1187 states the crisp rice per 30 g serving, and specification S-3120 states the almond butter per 32 g serving. The Specs tab converts both to 100 g before use; taken as per 100 g they would understate the sodium from the crisp rice and the fat from the almond butter by more than two thirds. The pilot batch lost 12.72 kg in the bake, so every nutrient is carried into a finished batch weight of 107.28 kg at a yield of 0.8940. A bar at 42 grams carries the nutrients of 46.98 grams of formula.</t>
+  </si>
+  <si>
+    <t>The nutrient sheet is out of date against three specifications in force, and section 1.2 says the specification in force governs. Its cherries row is still S-3301 revision 4, with total sugars at 58.0 g per 100 g and no added sugars figure; revision 5 puts 30.0 g of the 60.0 g of sugars per 100 g as added, the sucrose taken up in the infusion. Its brown rice syrup row is still S-2210 revision 2 at 43 mg of sodium per 100 g, and revision 3 states 2 mg after the plant move. Its vanilla extract row is still S-5020 revision 1 with no added sugar, and revision 2 states 12.7 g of added sugar per 100 g. With the syrup, the honey, the cherries and the vanilla the bar carries 7.929 g of added sugars unrounded, declared as 8 g at 16 percent of the daily value, against 9.490 g of total sugars declared as 9 g. Taken from the nutrient sheet rows, the added sugars line would print 7 g, and the sodium per serving would exceed 140 mg. The percent daily values are computed from the declared, rounded amount under section 3.1, which is why the added sugars line shows 16 percent and not 15.9.</t>
+  </si>
+  <si>
+    <t>The ingredient statement lists twelve ingredients in descending order of formula weight with water left off under section 4.1, each under its common name on the formula, and it reads: Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract (vanilla bean extractives in water and alcohol, sugar, natural flavor), ground cinnamon, sea salt (sea salt, calcium silicate), soy lecithin. Four compound ingredients carry the sub-ingredients their specifications list, S-1187 revision 7 for the crisp rice, S-3301 revision 5 for the cherries, S-5020 revision 2 for the vanilla extract and S-5040 revision 1 for the sea salt. Purchasing's line in the brief that the cherries and the crisp rice are the only compound items does not hold on two counts: S-5020 describes a two-fold extract with sugar and a natural flavor, and S-5040 lists calcium silicate as an anticaking agent after the salt. The Contains statement reads Contains almonds and soy; the barley malt extract in the crisp rice is a gluten source and not a major food allergen, and S-1187 states that none is present in the product.</t>
+  </si>
+  <si>
+    <t>On the claims. Good source of fiber is not supported, and it is close. The panel declares 3 g of fiber at 11 percent of the daily value, because the declared value rounds up from 2.823 g, but section 5.1 tests the claim on the unrounded amount per reference amount and per serving. The bar carries 2.823 g per 42 gram serving, which is 10.1 percent of the daily value and clears. It carries 2.689 g per 40 g reference amount, which is 9.6 percent and does not, and section 5.1 requires both bases. Low sodium is supported at 131.8 mg per reference amount and 138.4 mg per serving against the 140 mg ceiling. It holds only because the syrup is read at revision 3 and the yield at the scale ticket; on the nutrient sheet's 43 mg or on the bar-count weight the serving would exceed the ceiling.</t>
+  </si>
+  <si>
+    <t>Made with whole grain oats is not supported. The oats alone carry 14.80 g of whole grain into the bar against the 15 gram floor in section 5.3, and the brown rice syrup, which S-2210 describes as made from whole grain brown rice, is a derivative of a whole grain that section 5.3 excludes; counted in, it would lift the figure to 21.61 g, and that is the reading section 5.3 forbids. No artificial flavors is supported; the flavorings in the formula are the vanilla extract, which specification S-5020 states carries natural vanillin and a natural flavor only, and the barley malt extract inside the crisp rice. Real fruit is supported on the dried tart cherries, 3.76 g per bar. No added sugar is not supported and cannot be: the formula adds brown rice syrup, honey, sugar-infused cherries, a sweetened vanilla extract and a crisp rice that carries sugar of its own, and the panel declares 8 g of added sugars, so section 5.2 rules the flag out however it is worded. Two lines sit on a boundary. Calcium prints as 0 mg at 0 percent: the bar carries 25.389 mg, which is 1.95 percent of the daily value, and section 2.6 makes the 2 percent test on the unrounded amount before rounding; rounded first it would print 30 mg at 2 percent. Saturated fat prints as 0 g: the bar carries 0.498 g, under the 0.5 gram line in section 2.2 by two thousandths of a gram, so any rounding before the final sum would print 0.5 g.</t>
+  </si>
+  <si>
+    <t>Things for you to decide or take to a supplier before the copy locks. First, the fiber claim comes off the front panel unless product development reopens the frozen formula; it clears per serving and misses per reference amount by 0.11 g, so a small lift in the oats would carry it. Second, the no added sugar flag comes off; the sales lead should hear the 8 g figure rather than a softer claim. Third, the whole grain statement comes off as the formula stands, 0.20 g short of the floor on the oats alone. Fourth, the September 2025 crisp rice lots: purchasing's receiving log puts 1,800 kg of the launch inventory in lots packed under revision 6, which carry the declaration rice, sugar, salt, malt flavor and 140 mg of sodium per 30 g. On those lots the bar carries 145.3 mg of sodium per serving, the panel would print 150 mg, the statement would read malt flavor, and the low sodium flag fails, so none of the three holds for all launch inventory. Those lots either go to another product or the wrapper waits for them to be used up, and that is your call with purchasing. Fifth, purchasing should reissue the nutrient sheet with the cherries, the syrup and the vanilla at their revisions in force and with the serving weights beside the two per serving rows, and correct the brief's line on compound items for the vanilla and the salt. Sixth, the Contains statement rests on the formula and the specifications, and wheat, barley and peanuts do not belong in it. S-1187 says the crisp rice packing line also runs a wheat flake cereal, and S-3120 says the almond butter line runs peanut butter on alternate weeks. QA should decide whether a shared-line advisory prints under the Contains statement before the wrapper goes. The workbook cites every specification revision it used on the Specs tab.</t>
   </si>
 </sst>
 </file>
@@ -825,7 +904,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -847,6 +926,11 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1149,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1230,14 +1314,14 @@
       </c>
       <c r="B8" s="3">
         <f>Rounding!E5</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="4">
         <f>Rounding!G5</f>
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
@@ -1249,14 +1333,14 @@
       </c>
       <c r="B9" s="3">
         <f>Rounding!E6</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="4">
         <f>Rounding!G6</f>
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -1321,7 +1405,7 @@
       </c>
       <c r="B13" s="3">
         <f>Rounding!E10</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -1488,7 +1572,7 @@
       </c>
       <c r="B22" t="str">
         <f>'Ingredient Statement'!B17</f>
-        <v>Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract (vanilla bean extractives in water and alcohol, sugar, natural flavor), ground cinnamon, sea salt, soy lecithin.</v>
+        <v>Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract (vanilla bean extractives in water and alcohol, sugar, natural flavor), ground cinnamon, sea salt (sea salt, calcium silicate), soy lecithin.</v>
       </c>
       <c r="E22" t="s">
         <v>32</v>
@@ -1512,7 +1596,7 @@
       </c>
       <c r="B24">
         <f>Claims!B11</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" t="s">
         <v>35</v>
@@ -1524,15 +1608,51 @@
       </c>
       <c r="B25">
         <f>Claims!B12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="s">
         <v>35</v>
       </c>
     </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="str">
+        <f>'Inventory Check'!B13</f>
+        <v>No</v>
+      </c>
+      <c r="E26" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="B27" t="str">
+        <f>'Inventory Check'!B14</f>
+        <v>No</v>
+      </c>
+      <c r="E27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" t="str">
+        <f>'Inventory Check'!B15</f>
+        <v>No</v>
+      </c>
+      <c r="E28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1542,6 +1662,197 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="44" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C4">
+        <v>4200</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>96</v>
+      </c>
+      <c r="F4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5">
+        <v>1800</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>140</v>
+      </c>
+      <c r="F5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8">
+        <f>Nutrients!I17</f>
+        <v>138.3824</v>
+      </c>
+      <c r="C8">
+        <f>ROUND(Nutrients!I17-Nutrients!I6+ROUND(Nutrients!C6/100*ROUND(E5/30*100,4),4),4)</f>
+        <v>145.2728</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B9">
+        <f>Rounding!E9</f>
+        <v>140</v>
+      </c>
+      <c r="C9">
+        <f>IF(C8&lt;5,0,IF(C8&lt;=140,ROUND(C8/5,0)*5,ROUND(C8/10,0)*10))</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>258</v>
+      </c>
+      <c r="B10" t="str">
+        <f>IF(B8&lt;=Parameters!B13,"Supported","Not supported")</f>
+        <v>Supported</v>
+      </c>
+      <c r="C10" t="str">
+        <f>IF(C8&lt;=Parameters!B13,"Supported","Not supported")</f>
+        <v>Not supported</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B11" t="str">
+        <f>'Ingredient Statement'!E6</f>
+        <v>crisp rice (rice, sugar, barley malt extract, salt)</v>
+      </c>
+      <c r="C11" t="str">
+        <f>"crisp rice ("&amp;F5&amp;")"</f>
+        <v>crisp rice (rice, sugar, salt, malt flavor)</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="str">
+        <f>IF(C9=B9,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="str">
+        <f>IF(C11=B11,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="str">
+        <f>IF(AND(B10="Supported",C10="Supported"),"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A17:F17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1550,42 +1861,42 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -1595,7 +1906,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -1605,161 +1916,161 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B4">
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <f>'Pilot Batch Record'!B11</f>
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B6">
         <f>'Pilot Batch Record'!B4</f>
         <v>120</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B7">
         <f>'Pilot Batch Record'!B8</f>
         <v>107.28</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B8" s="7">
         <f>ROUND(B7/B6,4)</f>
         <v>0.894</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B9" s="8">
         <f>ROUND(B5/B7*B6,2)</f>
         <v>46.98</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B10" s="7">
         <f>ROUND(B5/B4,4)</f>
         <v>1.05</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B11" s="4">
         <v>0.1</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>0.2</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B13">
         <v>140</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B14">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>4</v>
@@ -1895,6 +2206,18 @@
       </c>
       <c r="C28" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="15">
+        <f>'Pilot Batch Record'!B9*B5</f>
+        <v>105840</v>
+      </c>
+      <c r="C30" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1914,125 +2237,125 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B4">
         <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B6">
         <v>108.14</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B7">
         <v>0.86</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>107.28</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B9">
-        <v>2548</v>
+        <v>2520</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B10">
         <v>42.1</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B11">
         <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B12">
         <v>8.6</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B13">
         <v>0.58</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2058,51 +2381,51 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C4" s="9">
-        <v>39.6</v>
+        <v>37.8</v>
       </c>
       <c r="D4" s="14">
         <f t="shared" ref="D4:D16" si="0">ROUND(C4/$C$17,5)</f>
-        <v>0.33</v>
+        <v>0.315</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" ref="E4:E10" si="1">LOWER(B4)</f>
@@ -2110,11 +2433,11 @@
       </c>
       <c r="G4" s="7">
         <f>ROUND(C4/Parameters!$B$7*Parameters!$B$5,4)</f>
-        <v>15.5034</v>
+        <v>14.7987</v>
       </c>
       <c r="H4" s="7">
         <f>ROUND(C4/Parameters!$B$7*Parameters!$B$4,4)</f>
-        <v>14.7651</v>
+        <v>14.094</v>
       </c>
       <c r="I4">
         <f t="shared" ref="I4:I16" si="2">RANK(C4,$C$4:$C$16)</f>
@@ -2123,10 +2446,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C5" s="9">
         <v>17.4</v>
@@ -2154,10 +2477,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C6" s="9">
         <v>12</v>
@@ -2171,7 +2494,7 @@
         <v>crisp rice</v>
       </c>
       <c r="F6" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G6" s="7">
         <f>ROUND(C6/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2188,10 +2511,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C7" s="9">
         <v>10.2</v>
@@ -2219,10 +2542,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C8" s="9">
         <v>9.6</v>
@@ -2236,7 +2559,7 @@
         <v>infused dried cherries</v>
       </c>
       <c r="F8" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G8" s="7">
         <f>ROUND(C8/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2253,10 +2576,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C9" s="9">
         <v>8.4</v>
@@ -2279,15 +2602,15 @@
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C10" s="9">
         <v>7.8</v>
@@ -2310,52 +2633,52 @@
       </c>
       <c r="I10">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C11" s="9">
-        <v>5.91</v>
+        <v>9.12</v>
       </c>
       <c r="D11" s="14">
         <f t="shared" si="0"/>
-        <v>0.04925</v>
+        <v>0.076</v>
       </c>
       <c r="E11" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G11" s="7">
         <f>ROUND(C11/Parameters!$B$7*Parameters!$B$5,4)</f>
-        <v>2.3138</v>
+        <v>3.5705</v>
       </c>
       <c r="H11" s="7">
         <f>ROUND(C11/Parameters!$B$7*Parameters!$B$4,4)</f>
-        <v>2.2036</v>
+        <v>3.4004</v>
       </c>
       <c r="I11">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C12" s="9">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="D12" s="14">
         <f t="shared" si="0"/>
-        <v>0.045</v>
+        <v>0.03333</v>
       </c>
       <c r="E12" t="str">
         <f>LOWER(B12)</f>
@@ -2363,11 +2686,11 @@
       </c>
       <c r="G12" s="7">
         <f>ROUND(C12/Parameters!$B$7*Parameters!$B$5,4)</f>
-        <v>2.1141</v>
+        <v>1.566</v>
       </c>
       <c r="H12" s="7">
         <f>ROUND(C12/Parameters!$B$7*Parameters!$B$4,4)</f>
-        <v>2.0134</v>
+        <v>1.4914</v>
       </c>
       <c r="I12">
         <f t="shared" si="2"/>
@@ -2376,10 +2699,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C13" s="9">
         <v>1.56</v>
@@ -2393,7 +2716,7 @@
         <v>vanilla extract</v>
       </c>
       <c r="F13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G13" s="7">
         <f>ROUND(C13/Parameters!$B$7*Parameters!$B$5,4)</f>
@@ -2410,10 +2733,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C14" s="9">
         <v>0.84</v>
@@ -2441,29 +2764,32 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C15" s="9">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="D15" s="14">
         <f t="shared" si="0"/>
-        <v>0.00675</v>
+        <v>0.00667</v>
       </c>
       <c r="E15" t="str">
         <f>LOWER(B15)</f>
         <v>sea salt</v>
       </c>
+      <c r="F15" t="s">
+        <v>133</v>
+      </c>
       <c r="G15" s="7">
         <f>ROUND(C15/Parameters!$B$7*Parameters!$B$5,4)</f>
-        <v>0.3171</v>
+        <v>0.3132</v>
       </c>
       <c r="H15" s="7">
         <f>ROUND(C15/Parameters!$B$7*Parameters!$B$4,4)</f>
-        <v>0.302</v>
+        <v>0.2983</v>
       </c>
       <c r="I15">
         <f t="shared" si="2"/>
@@ -2472,10 +2798,10 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C16" s="9">
         <v>0.48</v>
@@ -2503,7 +2829,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C17" s="9">
         <f>ROUND(SUM(C4:C16),3)</f>
@@ -2520,12 +2846,12 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2548,122 +2874,122 @@
   <sheetData>
     <row r="1" spans="1:36" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="AJ3" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -2675,7 +3001,7 @@
         <v>6.5</v>
       </c>
       <c r="F4">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2690,7 +3016,7 @@
         <v>67.7</v>
       </c>
       <c r="K4">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -2714,7 +3040,7 @@
         <v>362</v>
       </c>
       <c r="S4" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="U4" t="str">
         <f t="shared" ref="U4:U16" si="0">A4</f>
@@ -2730,7 +3056,7 @@
       </c>
       <c r="X4" s="7">
         <f t="shared" ref="X4:X16" si="3">ROUND(F4/$C4*100,4)</f>
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="Y4" s="7">
         <f t="shared" ref="Y4:Y16" si="4">ROUND(G4/$C4*100,4)</f>
@@ -2750,7 +3076,7 @@
       </c>
       <c r="AC4" s="7">
         <f t="shared" ref="AC4:AC16" si="8">ROUND(K4/$C4*100,4)</f>
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="AD4" s="7">
         <f t="shared" ref="AD4:AD16" si="9">ROUND(L4/$C4*100,4)</f>
@@ -2783,10 +3109,10 @@
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -2837,7 +3163,7 @@
         <v>62</v>
       </c>
       <c r="S5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="0"/>
@@ -2906,10 +3232,10 @@
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -2960,7 +3286,7 @@
         <v>28</v>
       </c>
       <c r="S6" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="0"/>
@@ -3029,10 +3355,10 @@
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -3083,7 +3409,7 @@
         <v>52</v>
       </c>
       <c r="S7" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="0"/>
@@ -3152,10 +3478,10 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -3206,7 +3532,7 @@
         <v>380</v>
       </c>
       <c r="S8" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="U8" t="str">
         <f t="shared" si="0"/>
@@ -3275,10 +3601,10 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C9">
         <v>32</v>
@@ -3290,7 +3616,7 @@
         <v>17.8</v>
       </c>
       <c r="F9">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3329,7 +3655,7 @@
         <v>239</v>
       </c>
       <c r="S9" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="0"/>
@@ -3345,7 +3671,7 @@
       </c>
       <c r="X9" s="7">
         <f t="shared" si="3"/>
-        <v>4.0625</v>
+        <v>3.125</v>
       </c>
       <c r="Y9" s="7">
         <f t="shared" si="4"/>
@@ -3398,10 +3724,10 @@
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -3413,7 +3739,7 @@
         <v>49.9</v>
       </c>
       <c r="F10">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3452,7 +3778,7 @@
         <v>733</v>
       </c>
       <c r="S10" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="U10" t="str">
         <f t="shared" si="0"/>
@@ -3468,7 +3794,7 @@
       </c>
       <c r="X10" s="7">
         <f t="shared" si="3"/>
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Y10" s="7">
         <f t="shared" si="4"/>
@@ -3521,10 +3847,10 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -3575,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="U11" t="str">
         <f t="shared" si="0"/>
@@ -3644,10 +3970,10 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -3698,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="U12" t="str">
         <f t="shared" si="0"/>
@@ -3767,10 +4093,10 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -3821,7 +4147,7 @@
         <v>148</v>
       </c>
       <c r="S13" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="U13" t="str">
         <f t="shared" si="0"/>
@@ -3890,10 +4216,10 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -3944,7 +4270,7 @@
         <v>431</v>
       </c>
       <c r="S14" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="U14" t="str">
         <f t="shared" si="0"/>
@@ -4013,10 +4339,10 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -4067,7 +4393,7 @@
         <v>8</v>
       </c>
       <c r="S15" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="U15" t="str">
         <f t="shared" si="0"/>
@@ -4136,10 +4462,10 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -4190,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="U16" t="str">
         <f t="shared" si="0"/>
@@ -4259,12 +4585,12 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -4285,63 +4611,63 @@
   <sheetData>
     <row r="1" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
@@ -4355,19 +4681,19 @@
       </c>
       <c r="C4" s="7">
         <f>Formula!G4</f>
-        <v>15.5034</v>
+        <v>14.7987</v>
       </c>
       <c r="D4" s="7">
         <f>ROUND($C4/100*Specs!V4,4)</f>
-        <v>58.7579</v>
+        <v>56.0871</v>
       </c>
       <c r="E4" s="7">
         <f>ROUND($C4/100*Specs!W4,4)</f>
-        <v>1.0077</v>
+        <v>0.9619</v>
       </c>
       <c r="F4" s="7">
         <f>ROUND($C4/100*Specs!X4,4)</f>
-        <v>0.1705</v>
+        <v>0.1036</v>
       </c>
       <c r="G4" s="7">
         <f>ROUND($C4/100*Specs!Y4,4)</f>
@@ -4379,19 +4705,19 @@
       </c>
       <c r="I4" s="7">
         <f>ROUND($C4/100*Specs!AA4,4)</f>
-        <v>0.9302</v>
+        <v>0.8879</v>
       </c>
       <c r="J4" s="7">
         <f>ROUND($C4/100*Specs!AB4,4)</f>
-        <v>10.4958</v>
+        <v>10.0187</v>
       </c>
       <c r="K4" s="7">
         <f>ROUND($C4/100*Specs!AC4,4)</f>
-        <v>1.7674</v>
+        <v>1.7758</v>
       </c>
       <c r="L4" s="7">
         <f>ROUND($C4/100*Specs!AD4,4)</f>
-        <v>0.155</v>
+        <v>0.148</v>
       </c>
       <c r="M4" s="7">
         <f>ROUND($C4/100*Specs!AE4,4)</f>
@@ -4399,7 +4725,7 @@
       </c>
       <c r="N4" s="7">
         <f>ROUND($C4/100*Specs!AF4,4)</f>
-        <v>2.0464</v>
+        <v>1.9534</v>
       </c>
       <c r="O4" s="7">
         <f>ROUND($C4/100*Specs!AG4,4)</f>
@@ -4407,15 +4733,15 @@
       </c>
       <c r="P4" s="7">
         <f>ROUND($C4/100*Specs!AH4,4)</f>
-        <v>6.9765</v>
+        <v>6.6594</v>
       </c>
       <c r="Q4" s="7">
         <f>ROUND($C4/100*Specs!AI4,4)</f>
-        <v>0.6589</v>
+        <v>0.6289</v>
       </c>
       <c r="R4" s="7">
         <f>ROUND($C4/100*Specs!AJ4,4)</f>
-        <v>56.1223</v>
+        <v>53.5713</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
@@ -4737,7 +5063,7 @@
       </c>
       <c r="F9" s="7">
         <f>ROUND($C9/100*Specs!X9,4)</f>
-        <v>0.1336</v>
+        <v>0.1028</v>
       </c>
       <c r="G9" s="7">
         <f>ROUND($C9/100*Specs!Y9,4)</f>
@@ -4811,7 +5137,7 @@
       </c>
       <c r="F10" s="7">
         <f>ROUND($C10/100*Specs!X10,4)</f>
-        <v>0.116</v>
+        <v>0.1099</v>
       </c>
       <c r="G10" s="7">
         <f>ROUND($C10/100*Specs!Y10,4)</f>
@@ -4873,7 +5199,7 @@
       </c>
       <c r="C11" s="7">
         <f>Formula!G11</f>
-        <v>2.3138</v>
+        <v>3.5705</v>
       </c>
       <c r="D11" s="7">
         <f>ROUND($C11/100*Specs!V11,4)</f>
@@ -4947,19 +5273,19 @@
       </c>
       <c r="C12" s="7">
         <f>Formula!G12</f>
-        <v>2.1141</v>
+        <v>1.566</v>
       </c>
       <c r="D12" s="7">
         <f>ROUND($C12/100*Specs!V12,4)</f>
-        <v>18.6886</v>
+        <v>13.8434</v>
       </c>
       <c r="E12" s="7">
         <f>ROUND($C12/100*Specs!W12,4)</f>
-        <v>2.1141</v>
+        <v>1.566</v>
       </c>
       <c r="F12" s="7">
         <f>ROUND($C12/100*Specs!X12,4)</f>
-        <v>0.1797</v>
+        <v>0.1331</v>
       </c>
       <c r="G12" s="7">
         <f>ROUND($C12/100*Specs!Y12,4)</f>
@@ -5169,7 +5495,7 @@
       </c>
       <c r="C15" s="7">
         <f>Formula!G15</f>
-        <v>0.3171</v>
+        <v>0.3132</v>
       </c>
       <c r="D15" s="7">
         <f>ROUND($C15/100*Specs!V15,4)</f>
@@ -5193,7 +5519,7 @@
       </c>
       <c r="I15" s="7">
         <f>ROUND($C15/100*Specs!AA15,4)</f>
-        <v>122.9016</v>
+        <v>121.3901</v>
       </c>
       <c r="J15" s="7">
         <f>ROUND($C15/100*Specs!AB15,4)</f>
@@ -5221,7 +5547,7 @@
       </c>
       <c r="P15" s="7">
         <f>ROUND($C15/100*Specs!AH15,4)</f>
-        <v>0.0761</v>
+        <v>0.0752</v>
       </c>
       <c r="Q15" s="7">
         <f>ROUND($C15/100*Specs!AI15,4)</f>
@@ -5229,7 +5555,7 @@
       </c>
       <c r="R15" s="7">
         <f>ROUND($C15/100*Specs!AJ15,4)</f>
-        <v>0.0254</v>
+        <v>0.0251</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -5308,7 +5634,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C17" s="7">
         <f>ROUND(SUM(C4:C16),4)</f>
@@ -5316,15 +5642,15 @@
       </c>
       <c r="D17" s="7">
         <f t="shared" ref="D17:R17" si="0">SUM(D4:D16)</f>
-        <v>183.6219</v>
+        <v>176.1059</v>
       </c>
       <c r="E17" s="7">
         <f t="shared" si="0"/>
-        <v>6.7655</v>
+        <v>6.1716</v>
       </c>
       <c r="F17" s="7">
         <f t="shared" si="0"/>
-        <v>0.6485</v>
+        <v>0.4981</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" si="0"/>
@@ -5336,19 +5662,19 @@
       </c>
       <c r="I17" s="7">
         <f t="shared" si="0"/>
-        <v>139.9362</v>
+        <v>138.3824</v>
       </c>
       <c r="J17" s="7">
         <f t="shared" si="0"/>
-        <v>27.8126</v>
+        <v>27.3355</v>
       </c>
       <c r="K17" s="7">
         <f t="shared" si="0"/>
-        <v>2.8149</v>
+        <v>2.8233</v>
       </c>
       <c r="L17" s="7">
         <f t="shared" si="0"/>
-        <v>9.497</v>
+        <v>9.49</v>
       </c>
       <c r="M17" s="7">
         <f t="shared" si="0"/>
@@ -5356,7 +5682,7 @@
       </c>
       <c r="N17" s="7">
         <f t="shared" si="0"/>
-        <v>3.8276</v>
+        <v>3.7346</v>
       </c>
       <c r="O17" s="7">
         <f t="shared" si="0"/>
@@ -5364,32 +5690,32 @@
       </c>
       <c r="P17" s="7">
         <f t="shared" si="0"/>
-        <v>25.7069</v>
+        <v>25.3889</v>
       </c>
       <c r="Q17" s="7">
         <f t="shared" si="0"/>
-        <v>1.0302</v>
+        <v>1.0002</v>
       </c>
       <c r="R17" s="7">
         <f t="shared" si="0"/>
-        <v>130.3811</v>
+        <v>127.8298</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D18" s="7">
         <f>ROUND(D17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>174.878</v>
+        <v>167.7199</v>
       </c>
       <c r="E18" s="7">
         <f>ROUND(E17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>6.4433</v>
+        <v>5.8777</v>
       </c>
       <c r="F18" s="7">
         <f>ROUND(F17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>0.6176</v>
+        <v>0.4744</v>
       </c>
       <c r="G18" s="7">
         <f>ROUND(G17*Parameters!$B$4/Parameters!$B$5,4)</f>
@@ -5401,19 +5727,19 @@
       </c>
       <c r="I18" s="7">
         <f>ROUND(I17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>133.2726</v>
+        <v>131.7928</v>
       </c>
       <c r="J18" s="7">
         <f>ROUND(J17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>26.4882</v>
+        <v>26.0338</v>
       </c>
       <c r="K18" s="7">
         <f>ROUND(K17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>2.6809</v>
+        <v>2.6889</v>
       </c>
       <c r="L18" s="7">
         <f>ROUND(L17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>9.0448</v>
+        <v>9.0381</v>
       </c>
       <c r="M18" s="7">
         <f>ROUND(M17*Parameters!$B$4/Parameters!$B$5,4)</f>
@@ -5421,7 +5747,7 @@
       </c>
       <c r="N18" s="7">
         <f>ROUND(N17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>3.6453</v>
+        <v>3.5568</v>
       </c>
       <c r="O18" s="7">
         <f>ROUND(O17*Parameters!$B$4/Parameters!$B$5,4)</f>
@@ -5429,20 +5755,20 @@
       </c>
       <c r="P18" s="7">
         <f>ROUND(P17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>24.4828</v>
+        <v>24.1799</v>
       </c>
       <c r="Q18" s="7">
         <f>ROUND(Q17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>0.9811</v>
+        <v>0.9526</v>
       </c>
       <c r="R18" s="7">
         <f>ROUND(R17*Parameters!$B$4/Parameters!$B$5,4)</f>
-        <v>124.1725</v>
+        <v>121.7427</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -5465,7 +5791,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -5476,22 +5802,22 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -5500,10 +5826,10 @@
       </c>
       <c r="C4" s="7">
         <f>Nutrients!D17</f>
-        <v>183.6219</v>
+        <v>176.1059</v>
       </c>
       <c r="D4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E4" s="3">
         <f>IF(C4&lt;5,0,IF(C4&lt;=50,ROUND(C4/5,0)*5,ROUND(C4/10,0)*10))</f>
@@ -5519,14 +5845,14 @@
       </c>
       <c r="C5" s="7">
         <f>Nutrients!E17</f>
-        <v>6.7655</v>
+        <v>6.1716</v>
       </c>
       <c r="D5" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E5" s="3">
         <f>IF(C5&lt;0.5,0,IF(C5&lt;5,ROUND(C5/0.5,0)*0.5,ROUND(C5,0)))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <f>Parameters!B17</f>
@@ -5534,11 +5860,11 @@
       </c>
       <c r="G5" s="4">
         <f>IF(ISNUMBER(E5),ROUND(E5/F5,2),ROUND(C5/F5,2))</f>
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H5" s="10">
         <f>ROUND(C5/F5,3)</f>
-        <v>0.087</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -5550,14 +5876,14 @@
       </c>
       <c r="C6" s="7">
         <f>Nutrients!F17</f>
-        <v>0.6485</v>
+        <v>0.4981</v>
       </c>
       <c r="D6" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E6" s="3">
         <f>IF(C6&lt;0.5,0,IF(C6&lt;5,ROUND(C6/0.5,0)*0.5,ROUND(C6,0)))</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <f>Parameters!B18</f>
@@ -5565,11 +5891,11 @@
       </c>
       <c r="G6" s="4">
         <f>IF(ISNUMBER(E6),ROUND(E6/F6,2),ROUND(C6/F6,2))</f>
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H6" s="10">
         <f>ROUND(C6/F6,3)</f>
-        <v>0.032</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -5584,7 +5910,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E7" s="3">
         <f>IF(C7&lt;0.5,0,IF(C7&lt;5,ROUND(C7/0.5,0)*0.5,ROUND(C7,0)))</f>
@@ -5603,7 +5929,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E8" s="3">
         <f>IF(C8&lt;2,0,IF(C8&lt;=5,"less than 5",ROUND(C8/5,0)*5))</f>
@@ -5631,10 +5957,10 @@
       </c>
       <c r="C9" s="7">
         <f>Nutrients!I17</f>
-        <v>139.9362</v>
+        <v>138.3824</v>
       </c>
       <c r="D9" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E9" s="3">
         <f>IF(C9&lt;5,0,IF(C9&lt;=140,ROUND(C9/5,0)*5,ROUND(C9/10,0)*10))</f>
@@ -5650,7 +5976,7 @@
       </c>
       <c r="H9" s="10">
         <f>ROUND(C9/F9,3)</f>
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -5662,14 +5988,14 @@
       </c>
       <c r="C10" s="7">
         <f>Nutrients!J17</f>
-        <v>27.8126</v>
+        <v>27.3355</v>
       </c>
       <c r="D10" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E10" s="3">
         <f>IF(C10&lt;0.5,0,IF(C10&lt;1,"less than 1",ROUND(C10,0)))</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10">
         <f>Parameters!B21</f>
@@ -5681,7 +6007,7 @@
       </c>
       <c r="H10" s="10">
         <f>ROUND(C10/F10,3)</f>
-        <v>0.101</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -5693,10 +6019,10 @@
       </c>
       <c r="C11" s="7">
         <f>Nutrients!K17</f>
-        <v>2.8149</v>
+        <v>2.8233</v>
       </c>
       <c r="D11" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E11" s="3">
         <f>IF(C11&lt;0.5,0,IF(C11&lt;1,"less than 1",ROUND(C11,0)))</f>
@@ -5724,10 +6050,10 @@
       </c>
       <c r="C12" s="7">
         <f>Nutrients!L17</f>
-        <v>9.497</v>
+        <v>9.49</v>
       </c>
       <c r="D12" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E12" s="3">
         <f>IF(C12&lt;0.5,0,IF(C12&lt;1,"less than 1",ROUND(C12,0)))</f>
@@ -5746,7 +6072,7 @@
         <v>7.929</v>
       </c>
       <c r="D13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E13" s="3">
         <f>IF(C13&lt;0.5,0,IF(C13&lt;1,"less than 1",ROUND(C13,0)))</f>
@@ -5774,10 +6100,10 @@
       </c>
       <c r="C14" s="7">
         <f>Nutrients!N17</f>
-        <v>3.8276</v>
+        <v>3.7346</v>
       </c>
       <c r="D14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E14" s="3">
         <f>IF(C14&lt;0.5,0,IF(C14&lt;1,"less than 1",ROUND(C14,0)))</f>
@@ -5793,7 +6119,7 @@
       </c>
       <c r="H14" s="10">
         <f t="shared" si="1"/>
-        <v>0.077</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -5808,7 +6134,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
         <f>IF(C15/F15&lt;0.02,0,ROUND(C15,1))</f>
@@ -5836,10 +6162,10 @@
       </c>
       <c r="C16" s="7">
         <f>Nutrients!P17</f>
-        <v>25.7069</v>
+        <v>25.3889</v>
       </c>
       <c r="D16" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E16" s="3">
         <f>IF(C16/F16&lt;0.02,0,ROUND(C16/10,0)*10)</f>
@@ -5867,10 +6193,10 @@
       </c>
       <c r="C17" s="7">
         <f>Nutrients!Q17</f>
-        <v>1.0302</v>
+        <v>1.0002</v>
       </c>
       <c r="D17" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E17" s="3">
         <f>IF(C17/F17&lt;0.02,0,ROUND(C17,1))</f>
@@ -5886,7 +6212,7 @@
       </c>
       <c r="H17" s="10">
         <f t="shared" si="1"/>
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -5898,10 +6224,10 @@
       </c>
       <c r="C18" s="7">
         <f>Nutrients!R17</f>
-        <v>130.3811</v>
+        <v>127.8298</v>
       </c>
       <c r="D18" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E18" s="3">
         <f>IF(C18/F18&lt;0.02,0,ROUND(C18/10,0)*10)</f>
@@ -5917,12 +6243,12 @@
       </c>
       <c r="H18" s="10">
         <f t="shared" si="1"/>
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -5945,27 +6271,27 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -5978,7 +6304,7 @@
       </c>
       <c r="C4" s="9">
         <f>Formula!C4</f>
-        <v>39.6</v>
+        <v>37.8</v>
       </c>
       <c r="D4" t="str">
         <f>IF(Formula!F4="","",Formula!F4)</f>
@@ -6094,7 +6420,7 @@
         <v>roasted almond butter</v>
       </c>
       <c r="F9" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -6118,7 +6444,7 @@
         <v>sliced almonds</v>
       </c>
       <c r="F10" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -6131,7 +6457,7 @@
       </c>
       <c r="C11" s="9">
         <f>Formula!C12</f>
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="D11" t="str">
         <f>IF(Formula!F12="","",Formula!F12)</f>
@@ -6194,15 +6520,15 @@
       </c>
       <c r="C14" s="9">
         <f>Formula!C15</f>
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="D14" t="str">
         <f>IF(Formula!F15="","",Formula!F15)</f>
-        <v/>
+        <v>sea salt, calcium silicate</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
-        <v>sea salt</v>
+        <v>sea salt (sea salt, calcium silicate)</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -6226,21 +6552,21 @@
         <v>soy lecithin</v>
       </c>
       <c r="F15" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B17" t="str">
         <f>UPPER(LEFT(E4&amp;", "&amp;E5&amp;", "&amp;E6&amp;", "&amp;E7&amp;", "&amp;E8&amp;", "&amp;E9&amp;", "&amp;E10&amp;", "&amp;E11&amp;", "&amp;E12&amp;", "&amp;E13&amp;", "&amp;E14&amp;", "&amp;E15,1))&amp;MID(E4&amp;", "&amp;E5&amp;", "&amp;E6&amp;", "&amp;E7&amp;", "&amp;E8&amp;", "&amp;E9&amp;", "&amp;E10&amp;", "&amp;E11&amp;", "&amp;E12&amp;", "&amp;E13&amp;", "&amp;E14&amp;", "&amp;E15,2,900)&amp;"."</f>
-        <v>Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract (vanilla bean extractives in water and alcohol, sugar, natural flavor), ground cinnamon, sea salt, soy lecithin.</v>
+        <v>Whole grain rolled oats, brown rice syrup, crisp rice (rice, sugar, barley malt extract, salt), clover honey, infused dried cherries (tart cherries, sugar, sunflower oil), roasted almond butter, sliced almonds, high oleic sunflower oil, vanilla extract (vanilla bean extractives in water and alcohol, sugar, natural flavor), ground cinnamon, sea salt (sea salt, calcium silicate), soy lecithin.</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B18" t="str">
         <f>"Contains: "&amp;IF(COUNTIF(F4:F15,"almonds")&gt;0,"almonds","")&amp;IF(COUNTIF(F4:F15,"soy")&gt;0,", soy","")&amp;"."</f>
@@ -6249,7 +6575,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B19">
         <f>COUNTA(B4:B15)</f>
@@ -6258,7 +6584,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -6282,43 +6608,43 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C4" s="11">
         <f>Parameters!$B$11*100</f>
@@ -6337,15 +6663,15 @@
         <v>Not supported</v>
       </c>
       <c r="G4" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B5" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C5" s="11">
         <f>Parameters!$B$13</f>
@@ -6353,26 +6679,26 @@
       </c>
       <c r="D5" s="11">
         <f>ROUND(Nutrients!I18,1)</f>
-        <v>133.3</v>
+        <v>131.8</v>
       </c>
       <c r="E5" s="11">
         <f>ROUND(Nutrients!I17,1)</f>
-        <v>139.9</v>
+        <v>138.4</v>
       </c>
       <c r="F5" t="str">
         <f>IF(AND(D5&lt;=C5,E5&lt;=C5),"Supported","Not supported")</f>
         <v>Supported</v>
       </c>
       <c r="G5" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B6" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C6" s="8">
         <f>Parameters!$B$14</f>
@@ -6381,37 +6707,37 @@
       <c r="D6" s="8"/>
       <c r="E6" s="8">
         <f>ROUND(Formula!G4,2)</f>
-        <v>15.5</v>
+        <v>14.8</v>
       </c>
       <c r="F6" t="str">
         <f>IF(E6&gt;=C6,"Supported","Not supported")</f>
-        <v>Supported</v>
+        <v>Not supported</v>
       </c>
       <c r="G6" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="F7" t="str">
         <f>IF(COUNTIF(Formula!B4:B16,"*artificial*")=0,"Supported","Not supported")</f>
         <v>Supported</v>
       </c>
       <c r="G7" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
@@ -6424,15 +6750,15 @@
         <v>Not supported</v>
       </c>
       <c r="G8" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B9" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -6445,16 +6771,16 @@
         <v>Supported</v>
       </c>
       <c r="G9" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B11">
         <f>COUNTIF(F4:F9,"Supported")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -6463,12 +6789,12 @@
       </c>
       <c r="B12">
         <f>COUNTIF(F4:F9,"Not supported")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
